--- a/config/data/ContentEvidenceBinding.xlsx
+++ b/config/data/ContentEvidenceBinding.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J797"/>
+  <dimension ref="A1:J802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -773,7 +773,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Observed</t>
+          <t>ExactStructured</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Observed</t>
+          <t>ExactStructured</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Observed</t>
+          <t>ExactStructured</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Observed</t>
+          <t>ExactStructured</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Observed</t>
+          <t>ExactStructured</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Observed</t>
+          <t>ExactStructured</t>
         </is>
       </c>
     </row>
@@ -18455,14 +18455,14 @@
     </row>
     <row r="543">
       <c r="B543" t="n">
-        <v>22001</v>
+        <v>21990</v>
       </c>
       <c r="C543" t="n">
         <v>1</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.01.trace-1</t>
+          <t>v1b.prepared:program.hit-plan.character.silver-wolf-lv-999.ability.bonus-stage-αwolf-instant.normal.phase-2</t>
         </is>
       </c>
       <c r="E543" t="n">
@@ -18484,14 +18484,14 @@
     </row>
     <row r="544">
       <c r="B544" t="n">
-        <v>22002</v>
+        <v>21991</v>
       </c>
       <c r="C544" t="n">
         <v>1</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.02.trace-2</t>
+          <t>v1b.prepared:program.hit-plan.character.silver-wolf-lv-999.ability.bonus-stage-αwolf-instant.normal.phase-3</t>
         </is>
       </c>
       <c r="E544" t="n">
@@ -18513,14 +18513,14 @@
     </row>
     <row r="545">
       <c r="B545" t="n">
-        <v>22003</v>
+        <v>21992</v>
       </c>
       <c r="C545" t="n">
         <v>1</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.03.trace-3</t>
+          <t>v1b.prepared:program.hit-plan.character.silver-wolf-lv-999.ability.bonus-stage-αwolf-instant.normal.phase-4</t>
         </is>
       </c>
       <c r="E545" t="n">
@@ -18542,14 +18542,14 @@
     </row>
     <row r="546">
       <c r="B546" t="n">
-        <v>22004</v>
+        <v>22001</v>
       </c>
       <c r="C546" t="n">
         <v>1</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.04.trace-4</t>
+          <t>v1b.prepared:character.aglaea.trace.01.trace-1</t>
         </is>
       </c>
       <c r="E546" t="n">
@@ -18571,14 +18571,14 @@
     </row>
     <row r="547">
       <c r="B547" t="n">
-        <v>22005</v>
+        <v>22002</v>
       </c>
       <c r="C547" t="n">
         <v>1</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.05.trace-5</t>
+          <t>v1b.prepared:character.aglaea.trace.02.trace-2</t>
         </is>
       </c>
       <c r="E547" t="n">
@@ -18600,14 +18600,14 @@
     </row>
     <row r="548">
       <c r="B548" t="n">
-        <v>22006</v>
+        <v>22003</v>
       </c>
       <c r="C548" t="n">
         <v>1</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.06.the-myopics-doom</t>
+          <t>v1b.prepared:character.aglaea.trace.03.trace-3</t>
         </is>
       </c>
       <c r="E548" t="n">
@@ -18629,14 +18629,14 @@
     </row>
     <row r="549">
       <c r="B549" t="n">
-        <v>22007</v>
+        <v>22004</v>
       </c>
       <c r="C549" t="n">
         <v>1</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.07.last-thread-of-fate</t>
+          <t>v1b.prepared:character.aglaea.trace.04.trace-4</t>
         </is>
       </c>
       <c r="E549" t="n">
@@ -18658,14 +18658,14 @@
     </row>
     <row r="550">
       <c r="B550" t="n">
-        <v>22008</v>
+        <v>22005</v>
       </c>
       <c r="C550" t="n">
         <v>1</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.08.the-speeding-sol</t>
+          <t>v1b.prepared:character.aglaea.trace.05.trace-5</t>
         </is>
       </c>
       <c r="E550" t="n">
@@ -18687,14 +18687,14 @@
     </row>
     <row r="551">
       <c r="B551" t="n">
-        <v>22009</v>
+        <v>22006</v>
       </c>
       <c r="C551" t="n">
         <v>1</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.09.dmg-boost-lightning</t>
+          <t>v1b.prepared:character.aglaea.trace.06.the-myopics-doom</t>
         </is>
       </c>
       <c r="E551" t="n">
@@ -18716,14 +18716,14 @@
     </row>
     <row r="552">
       <c r="B552" t="n">
-        <v>22010</v>
+        <v>22007</v>
       </c>
       <c r="C552" t="n">
         <v>1</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.10.crit-rate-boost</t>
+          <t>v1b.prepared:character.aglaea.trace.07.last-thread-of-fate</t>
         </is>
       </c>
       <c r="E552" t="n">
@@ -18745,14 +18745,14 @@
     </row>
     <row r="553">
       <c r="B553" t="n">
-        <v>22011</v>
+        <v>22008</v>
       </c>
       <c r="C553" t="n">
         <v>1</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.11.dmg-boost-lightning</t>
+          <t>v1b.prepared:character.aglaea.trace.08.the-speeding-sol</t>
         </is>
       </c>
       <c r="E553" t="n">
@@ -18774,14 +18774,14 @@
     </row>
     <row r="554">
       <c r="B554" t="n">
-        <v>22012</v>
+        <v>22009</v>
       </c>
       <c r="C554" t="n">
         <v>1</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.12.def-boost</t>
+          <t>v1b.prepared:character.aglaea.trace.09.dmg-boost-lightning</t>
         </is>
       </c>
       <c r="E554" t="n">
@@ -18803,14 +18803,14 @@
     </row>
     <row r="555">
       <c r="B555" t="n">
-        <v>22013</v>
+        <v>22010</v>
       </c>
       <c r="C555" t="n">
         <v>1</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.13.dmg-boost-lightning</t>
+          <t>v1b.prepared:character.aglaea.trace.10.crit-rate-boost</t>
         </is>
       </c>
       <c r="E555" t="n">
@@ -18832,14 +18832,14 @@
     </row>
     <row r="556">
       <c r="B556" t="n">
-        <v>22014</v>
+        <v>22011</v>
       </c>
       <c r="C556" t="n">
         <v>1</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.14.crit-rate-boost</t>
+          <t>v1b.prepared:character.aglaea.trace.11.dmg-boost-lightning</t>
         </is>
       </c>
       <c r="E556" t="n">
@@ -18861,14 +18861,14 @@
     </row>
     <row r="557">
       <c r="B557" t="n">
-        <v>22015</v>
+        <v>22012</v>
       </c>
       <c r="C557" t="n">
         <v>1</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.15.dmg-boost-lightning</t>
+          <t>v1b.prepared:character.aglaea.trace.12.def-boost</t>
         </is>
       </c>
       <c r="E557" t="n">
@@ -18890,14 +18890,14 @@
     </row>
     <row r="558">
       <c r="B558" t="n">
-        <v>22016</v>
+        <v>22013</v>
       </c>
       <c r="C558" t="n">
         <v>1</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.16.def-boost</t>
+          <t>v1b.prepared:character.aglaea.trace.13.dmg-boost-lightning</t>
         </is>
       </c>
       <c r="E558" t="n">
@@ -18919,14 +18919,14 @@
     </row>
     <row r="559">
       <c r="B559" t="n">
-        <v>22017</v>
+        <v>22014</v>
       </c>
       <c r="C559" t="n">
         <v>1</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.17.crit-rate-boost</t>
+          <t>v1b.prepared:character.aglaea.trace.14.crit-rate-boost</t>
         </is>
       </c>
       <c r="E559" t="n">
@@ -18948,14 +18948,14 @@
     </row>
     <row r="560">
       <c r="B560" t="n">
-        <v>22018</v>
+        <v>22015</v>
       </c>
       <c r="C560" t="n">
         <v>1</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.18.dmg-boost-lightning</t>
+          <t>v1b.prepared:character.aglaea.trace.15.dmg-boost-lightning</t>
         </is>
       </c>
       <c r="E560" t="n">
@@ -18977,14 +18977,14 @@
     </row>
     <row r="561">
       <c r="B561" t="n">
-        <v>22019</v>
+        <v>22016</v>
       </c>
       <c r="C561" t="n">
         <v>1</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.19.thorned-snare</t>
+          <t>v1b.prepared:character.aglaea.trace.16.def-boost</t>
         </is>
       </c>
       <c r="E561" t="n">
@@ -19006,14 +19006,14 @@
     </row>
     <row r="562">
       <c r="B562" t="n">
-        <v>22020</v>
+        <v>22017</v>
       </c>
       <c r="C562" t="n">
         <v>1</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.trace.20.a-body-brewed-by-tears</t>
+          <t>v1b.prepared:character.aglaea.trace.17.crit-rate-boost</t>
         </is>
       </c>
       <c r="E562" t="n">
@@ -19035,14 +19035,14 @@
     </row>
     <row r="563">
       <c r="B563" t="n">
-        <v>22021</v>
+        <v>22018</v>
       </c>
       <c r="C563" t="n">
         <v>1</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.01.trace-1</t>
+          <t>v1b.prepared:character.aglaea.trace.18.dmg-boost-lightning</t>
         </is>
       </c>
       <c r="E563" t="n">
@@ -19064,14 +19064,14 @@
     </row>
     <row r="564">
       <c r="B564" t="n">
-        <v>22022</v>
+        <v>22019</v>
       </c>
       <c r="C564" t="n">
         <v>1</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.02.trace-2</t>
+          <t>v1b.prepared:character.aglaea.trace.19.thorned-snare</t>
         </is>
       </c>
       <c r="E564" t="n">
@@ -19093,14 +19093,14 @@
     </row>
     <row r="565">
       <c r="B565" t="n">
-        <v>22023</v>
+        <v>22020</v>
       </c>
       <c r="C565" t="n">
         <v>1</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.03.trace-3</t>
+          <t>v1b.prepared:character.aglaea.trace.20.a-body-brewed-by-tears</t>
         </is>
       </c>
       <c r="E565" t="n">
@@ -19122,14 +19122,14 @@
     </row>
     <row r="566">
       <c r="B566" t="n">
-        <v>22024</v>
+        <v>22021</v>
       </c>
       <c r="C566" t="n">
         <v>1</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.04.trace-4</t>
+          <t>v1b.prepared:character.asta.trace.01.trace-1</t>
         </is>
       </c>
       <c r="E566" t="n">
@@ -19151,14 +19151,14 @@
     </row>
     <row r="567">
       <c r="B567" t="n">
-        <v>22025</v>
+        <v>22022</v>
       </c>
       <c r="C567" t="n">
         <v>1</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.05.trace-5</t>
+          <t>v1b.prepared:character.asta.trace.02.trace-2</t>
         </is>
       </c>
       <c r="E567" t="n">
@@ -19180,14 +19180,14 @@
     </row>
     <row r="568">
       <c r="B568" t="n">
-        <v>22026</v>
+        <v>22023</v>
       </c>
       <c r="C568" t="n">
         <v>1</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.06.sparks</t>
+          <t>v1b.prepared:character.asta.trace.03.trace-3</t>
         </is>
       </c>
       <c r="E568" t="n">
@@ -19209,14 +19209,14 @@
     </row>
     <row r="569">
       <c r="B569" t="n">
-        <v>22027</v>
+        <v>22024</v>
       </c>
       <c r="C569" t="n">
         <v>1</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.07.ignite</t>
+          <t>v1b.prepared:character.asta.trace.04.trace-4</t>
         </is>
       </c>
       <c r="E569" t="n">
@@ -19238,14 +19238,14 @@
     </row>
     <row r="570">
       <c r="B570" t="n">
-        <v>22028</v>
+        <v>22025</v>
       </c>
       <c r="C570" t="n">
         <v>1</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.08.constellation</t>
+          <t>v1b.prepared:character.asta.trace.05.trace-5</t>
         </is>
       </c>
       <c r="E570" t="n">
@@ -19267,14 +19267,14 @@
     </row>
     <row r="571">
       <c r="B571" t="n">
-        <v>22029</v>
+        <v>22026</v>
       </c>
       <c r="C571" t="n">
         <v>1</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.09.dmg-boost-fire</t>
+          <t>v1b.prepared:character.asta.trace.06.sparks</t>
         </is>
       </c>
       <c r="E571" t="n">
@@ -19296,14 +19296,14 @@
     </row>
     <row r="572">
       <c r="B572" t="n">
-        <v>22030</v>
+        <v>22027</v>
       </c>
       <c r="C572" t="n">
         <v>1</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.10.def-boost</t>
+          <t>v1b.prepared:character.asta.trace.07.ignite</t>
         </is>
       </c>
       <c r="E572" t="n">
@@ -19325,14 +19325,14 @@
     </row>
     <row r="573">
       <c r="B573" t="n">
-        <v>22031</v>
+        <v>22028</v>
       </c>
       <c r="C573" t="n">
         <v>1</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.11.dmg-boost-fire</t>
+          <t>v1b.prepared:character.asta.trace.08.constellation</t>
         </is>
       </c>
       <c r="E573" t="n">
@@ -19354,14 +19354,14 @@
     </row>
     <row r="574">
       <c r="B574" t="n">
-        <v>22032</v>
+        <v>22029</v>
       </c>
       <c r="C574" t="n">
         <v>1</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.12.crit-rate-boost</t>
+          <t>v1b.prepared:character.asta.trace.09.dmg-boost-fire</t>
         </is>
       </c>
       <c r="E574" t="n">
@@ -19383,14 +19383,14 @@
     </row>
     <row r="575">
       <c r="B575" t="n">
-        <v>22033</v>
+        <v>22030</v>
       </c>
       <c r="C575" t="n">
         <v>1</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.13.dmg-boost-fire</t>
+          <t>v1b.prepared:character.asta.trace.10.def-boost</t>
         </is>
       </c>
       <c r="E575" t="n">
@@ -19412,14 +19412,14 @@
     </row>
     <row r="576">
       <c r="B576" t="n">
-        <v>22034</v>
+        <v>22031</v>
       </c>
       <c r="C576" t="n">
         <v>1</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.14.def-boost</t>
+          <t>v1b.prepared:character.asta.trace.11.dmg-boost-fire</t>
         </is>
       </c>
       <c r="E576" t="n">
@@ -19441,14 +19441,14 @@
     </row>
     <row r="577">
       <c r="B577" t="n">
-        <v>22035</v>
+        <v>22032</v>
       </c>
       <c r="C577" t="n">
         <v>1</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.15.dmg-boost-fire</t>
+          <t>v1b.prepared:character.asta.trace.12.crit-rate-boost</t>
         </is>
       </c>
       <c r="E577" t="n">
@@ -19470,14 +19470,14 @@
     </row>
     <row r="578">
       <c r="B578" t="n">
-        <v>22036</v>
+        <v>22033</v>
       </c>
       <c r="C578" t="n">
         <v>1</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.16.crit-rate-boost</t>
+          <t>v1b.prepared:character.asta.trace.13.dmg-boost-fire</t>
         </is>
       </c>
       <c r="E578" t="n">
@@ -19499,14 +19499,14 @@
     </row>
     <row r="579">
       <c r="B579" t="n">
-        <v>22037</v>
+        <v>22034</v>
       </c>
       <c r="C579" t="n">
         <v>1</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.17.def-boost</t>
+          <t>v1b.prepared:character.asta.trace.14.def-boost</t>
         </is>
       </c>
       <c r="E579" t="n">
@@ -19528,14 +19528,14 @@
     </row>
     <row r="580">
       <c r="B580" t="n">
-        <v>22038</v>
+        <v>22035</v>
       </c>
       <c r="C580" t="n">
         <v>1</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.trace.18.dmg-boost-fire</t>
+          <t>v1b.prepared:character.asta.trace.15.dmg-boost-fire</t>
         </is>
       </c>
       <c r="E580" t="n">
@@ -19557,14 +19557,14 @@
     </row>
     <row r="581">
       <c r="B581" t="n">
-        <v>22039</v>
+        <v>22036</v>
       </c>
       <c r="C581" t="n">
         <v>1</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.01.trace-1</t>
+          <t>v1b.prepared:character.asta.trace.16.crit-rate-boost</t>
         </is>
       </c>
       <c r="E581" t="n">
@@ -19586,14 +19586,14 @@
     </row>
     <row r="582">
       <c r="B582" t="n">
-        <v>22040</v>
+        <v>22037</v>
       </c>
       <c r="C582" t="n">
         <v>1</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.02.trace-2</t>
+          <t>v1b.prepared:character.asta.trace.17.def-boost</t>
         </is>
       </c>
       <c r="E582" t="n">
@@ -19615,14 +19615,14 @@
     </row>
     <row r="583">
       <c r="B583" t="n">
-        <v>22041</v>
+        <v>22038</v>
       </c>
       <c r="C583" t="n">
         <v>1</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.03.trace-3</t>
+          <t>v1b.prepared:character.asta.trace.18.dmg-boost-fire</t>
         </is>
       </c>
       <c r="E583" t="n">
@@ -19644,14 +19644,14 @@
     </row>
     <row r="584">
       <c r="B584" t="n">
-        <v>22042</v>
+        <v>22039</v>
       </c>
       <c r="C584" t="n">
         <v>1</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.04.trace-4</t>
+          <t>v1b.prepared:character.clara.trace.01.trace-1</t>
         </is>
       </c>
       <c r="E584" t="n">
@@ -19673,14 +19673,14 @@
     </row>
     <row r="585">
       <c r="B585" t="n">
-        <v>22043</v>
+        <v>22040</v>
       </c>
       <c r="C585" t="n">
         <v>1</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.05.trace-5</t>
+          <t>v1b.prepared:character.clara.trace.02.trace-2</t>
         </is>
       </c>
       <c r="E585" t="n">
@@ -19702,14 +19702,14 @@
     </row>
     <row r="586">
       <c r="B586" t="n">
-        <v>22044</v>
+        <v>22041</v>
       </c>
       <c r="C586" t="n">
         <v>1</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.06.kinship</t>
+          <t>v1b.prepared:character.clara.trace.03.trace-3</t>
         </is>
       </c>
       <c r="E586" t="n">
@@ -19731,14 +19731,14 @@
     </row>
     <row r="587">
       <c r="B587" t="n">
-        <v>22045</v>
+        <v>22042</v>
       </c>
       <c r="C587" t="n">
         <v>1</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.07.under-protection</t>
+          <t>v1b.prepared:character.clara.trace.04.trace-4</t>
         </is>
       </c>
       <c r="E587" t="n">
@@ -19760,14 +19760,14 @@
     </row>
     <row r="588">
       <c r="B588" t="n">
-        <v>22046</v>
+        <v>22043</v>
       </c>
       <c r="C588" t="n">
         <v>1</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.08.revenge</t>
+          <t>v1b.prepared:character.clara.trace.05.trace-5</t>
         </is>
       </c>
       <c r="E588" t="n">
@@ -19789,14 +19789,14 @@
     </row>
     <row r="589">
       <c r="B589" t="n">
-        <v>22047</v>
+        <v>22044</v>
       </c>
       <c r="C589" t="n">
         <v>1</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.09.atk-boost</t>
+          <t>v1b.prepared:character.clara.trace.06.kinship</t>
         </is>
       </c>
       <c r="E589" t="n">
@@ -19818,14 +19818,14 @@
     </row>
     <row r="590">
       <c r="B590" t="n">
-        <v>22048</v>
+        <v>22045</v>
       </c>
       <c r="C590" t="n">
         <v>1</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.10.dmg-boost-physical</t>
+          <t>v1b.prepared:character.clara.trace.07.under-protection</t>
         </is>
       </c>
       <c r="E590" t="n">
@@ -19847,14 +19847,14 @@
     </row>
     <row r="591">
       <c r="B591" t="n">
-        <v>22049</v>
+        <v>22046</v>
       </c>
       <c r="C591" t="n">
         <v>1</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.11.atk-boost</t>
+          <t>v1b.prepared:character.clara.trace.08.revenge</t>
         </is>
       </c>
       <c r="E591" t="n">
@@ -19876,14 +19876,14 @@
     </row>
     <row r="592">
       <c r="B592" t="n">
-        <v>22050</v>
+        <v>22047</v>
       </c>
       <c r="C592" t="n">
         <v>1</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.12.hp-boost</t>
+          <t>v1b.prepared:character.clara.trace.09.atk-boost</t>
         </is>
       </c>
       <c r="E592" t="n">
@@ -19905,14 +19905,14 @@
     </row>
     <row r="593">
       <c r="B593" t="n">
-        <v>22051</v>
+        <v>22048</v>
       </c>
       <c r="C593" t="n">
         <v>1</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.13.atk-boost</t>
+          <t>v1b.prepared:character.clara.trace.10.dmg-boost-physical</t>
         </is>
       </c>
       <c r="E593" t="n">
@@ -19934,14 +19934,14 @@
     </row>
     <row r="594">
       <c r="B594" t="n">
-        <v>22052</v>
+        <v>22049</v>
       </c>
       <c r="C594" t="n">
         <v>1</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.14.dmg-boost-physical</t>
+          <t>v1b.prepared:character.clara.trace.11.atk-boost</t>
         </is>
       </c>
       <c r="E594" t="n">
@@ -19963,14 +19963,14 @@
     </row>
     <row r="595">
       <c r="B595" t="n">
-        <v>22053</v>
+        <v>22050</v>
       </c>
       <c r="C595" t="n">
         <v>1</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.15.atk-boost</t>
+          <t>v1b.prepared:character.clara.trace.12.hp-boost</t>
         </is>
       </c>
       <c r="E595" t="n">
@@ -19992,14 +19992,14 @@
     </row>
     <row r="596">
       <c r="B596" t="n">
-        <v>22054</v>
+        <v>22051</v>
       </c>
       <c r="C596" t="n">
         <v>1</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.16.hp-boost</t>
+          <t>v1b.prepared:character.clara.trace.13.atk-boost</t>
         </is>
       </c>
       <c r="E596" t="n">
@@ -20021,14 +20021,14 @@
     </row>
     <row r="597">
       <c r="B597" t="n">
-        <v>22055</v>
+        <v>22052</v>
       </c>
       <c r="C597" t="n">
         <v>1</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.17.dmg-boost-physical</t>
+          <t>v1b.prepared:character.clara.trace.14.dmg-boost-physical</t>
         </is>
       </c>
       <c r="E597" t="n">
@@ -20050,14 +20050,14 @@
     </row>
     <row r="598">
       <c r="B598" t="n">
-        <v>22056</v>
+        <v>22053</v>
       </c>
       <c r="C598" t="n">
         <v>1</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.trace.18.atk-boost</t>
+          <t>v1b.prepared:character.clara.trace.15.atk-boost</t>
         </is>
       </c>
       <c r="E598" t="n">
@@ -20079,14 +20079,14 @@
     </row>
     <row r="599">
       <c r="B599" t="n">
-        <v>22057</v>
+        <v>22054</v>
       </c>
       <c r="C599" t="n">
         <v>1</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.01.trace-1</t>
+          <t>v1b.prepared:character.clara.trace.16.hp-boost</t>
         </is>
       </c>
       <c r="E599" t="n">
@@ -20108,14 +20108,14 @@
     </row>
     <row r="600">
       <c r="B600" t="n">
-        <v>22058</v>
+        <v>22055</v>
       </c>
       <c r="C600" t="n">
         <v>1</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.02.trace-2</t>
+          <t>v1b.prepared:character.clara.trace.17.dmg-boost-physical</t>
         </is>
       </c>
       <c r="E600" t="n">
@@ -20137,14 +20137,14 @@
     </row>
     <row r="601">
       <c r="B601" t="n">
-        <v>22059</v>
+        <v>22056</v>
       </c>
       <c r="C601" t="n">
         <v>1</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.03.trace-3</t>
+          <t>v1b.prepared:character.clara.trace.18.atk-boost</t>
         </is>
       </c>
       <c r="E601" t="n">
@@ -20166,14 +20166,14 @@
     </row>
     <row r="602">
       <c r="B602" t="n">
-        <v>22060</v>
+        <v>22057</v>
       </c>
       <c r="C602" t="n">
         <v>1</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.04.trace-4</t>
+          <t>v1b.prepared:character.firefly.trace.01.trace-1</t>
         </is>
       </c>
       <c r="E602" t="n">
@@ -20195,14 +20195,14 @@
     </row>
     <row r="603">
       <c r="B603" t="n">
-        <v>22061</v>
+        <v>22058</v>
       </c>
       <c r="C603" t="n">
         <v>1</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.05.trace-5</t>
+          <t>v1b.prepared:character.firefly.trace.02.trace-2</t>
         </is>
       </c>
       <c r="E603" t="n">
@@ -20224,14 +20224,14 @@
     </row>
     <row r="604">
       <c r="B604" t="n">
-        <v>22062</v>
+        <v>22059</v>
       </c>
       <c r="C604" t="n">
         <v>1</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.06.module-α-antilag-outburst</t>
+          <t>v1b.prepared:character.firefly.trace.03.trace-3</t>
         </is>
       </c>
       <c r="E604" t="n">
@@ -20253,14 +20253,14 @@
     </row>
     <row r="605">
       <c r="B605" t="n">
-        <v>22063</v>
+        <v>22060</v>
       </c>
       <c r="C605" t="n">
         <v>1</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.07.module-α-antilag-outburst</t>
+          <t>v1b.prepared:character.firefly.trace.04.trace-4</t>
         </is>
       </c>
       <c r="E605" t="n">
@@ -20282,14 +20282,14 @@
     </row>
     <row r="606">
       <c r="B606" t="n">
-        <v>22064</v>
+        <v>22061</v>
       </c>
       <c r="C606" t="n">
         <v>1</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.08.module-β-autoreactive-armor</t>
+          <t>v1b.prepared:character.firefly.trace.05.trace-5</t>
         </is>
       </c>
       <c r="E606" t="n">
@@ -20311,14 +20311,14 @@
     </row>
     <row r="607">
       <c r="B607" t="n">
-        <v>22065</v>
+        <v>22062</v>
       </c>
       <c r="C607" t="n">
         <v>1</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.09.module-β-autoreactive-armor</t>
+          <t>v1b.prepared:character.firefly.trace.06.module-α-antilag-outburst</t>
         </is>
       </c>
       <c r="E607" t="n">
@@ -20340,14 +20340,14 @@
     </row>
     <row r="608">
       <c r="B608" t="n">
-        <v>22066</v>
+        <v>22063</v>
       </c>
       <c r="C608" t="n">
         <v>1</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.10.module-γ-core-overload</t>
+          <t>v1b.prepared:character.firefly.trace.07.module-α-antilag-outburst</t>
         </is>
       </c>
       <c r="E608" t="n">
@@ -20369,14 +20369,14 @@
     </row>
     <row r="609">
       <c r="B609" t="n">
-        <v>22067</v>
+        <v>22064</v>
       </c>
       <c r="C609" t="n">
         <v>1</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.11.module-γ-core-overload</t>
+          <t>v1b.prepared:character.firefly.trace.08.module-β-autoreactive-armor</t>
         </is>
       </c>
       <c r="E609" t="n">
@@ -20398,14 +20398,14 @@
     </row>
     <row r="610">
       <c r="B610" t="n">
-        <v>22068</v>
+        <v>22065</v>
       </c>
       <c r="C610" t="n">
         <v>1</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.12.break-boost</t>
+          <t>v1b.prepared:character.firefly.trace.09.module-β-autoreactive-armor</t>
         </is>
       </c>
       <c r="E610" t="n">
@@ -20427,14 +20427,14 @@
     </row>
     <row r="611">
       <c r="B611" t="n">
-        <v>22069</v>
+        <v>22066</v>
       </c>
       <c r="C611" t="n">
         <v>1</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.13.effect-res-boost</t>
+          <t>v1b.prepared:character.firefly.trace.10.module-γ-core-overload</t>
         </is>
       </c>
       <c r="E611" t="n">
@@ -20456,14 +20456,14 @@
     </row>
     <row r="612">
       <c r="B612" t="n">
-        <v>22070</v>
+        <v>22067</v>
       </c>
       <c r="C612" t="n">
         <v>1</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.14.break-boost</t>
+          <t>v1b.prepared:character.firefly.trace.11.module-γ-core-overload</t>
         </is>
       </c>
       <c r="E612" t="n">
@@ -20485,14 +20485,14 @@
     </row>
     <row r="613">
       <c r="B613" t="n">
-        <v>22071</v>
+        <v>22068</v>
       </c>
       <c r="C613" t="n">
         <v>1</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.15.spd-boost</t>
+          <t>v1b.prepared:character.firefly.trace.12.break-boost</t>
         </is>
       </c>
       <c r="E613" t="n">
@@ -20514,14 +20514,14 @@
     </row>
     <row r="614">
       <c r="B614" t="n">
-        <v>22072</v>
+        <v>22069</v>
       </c>
       <c r="C614" t="n">
         <v>1</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.16.break-boost</t>
+          <t>v1b.prepared:character.firefly.trace.13.effect-res-boost</t>
         </is>
       </c>
       <c r="E614" t="n">
@@ -20543,14 +20543,14 @@
     </row>
     <row r="615">
       <c r="B615" t="n">
-        <v>22073</v>
+        <v>22070</v>
       </c>
       <c r="C615" t="n">
         <v>1</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.17.effect-res-boost</t>
+          <t>v1b.prepared:character.firefly.trace.14.break-boost</t>
         </is>
       </c>
       <c r="E615" t="n">
@@ -20572,14 +20572,14 @@
     </row>
     <row r="616">
       <c r="B616" t="n">
-        <v>22074</v>
+        <v>22071</v>
       </c>
       <c r="C616" t="n">
         <v>1</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.18.break-boost</t>
+          <t>v1b.prepared:character.firefly.trace.15.spd-boost</t>
         </is>
       </c>
       <c r="E616" t="n">
@@ -20601,14 +20601,14 @@
     </row>
     <row r="617">
       <c r="B617" t="n">
-        <v>22075</v>
+        <v>22072</v>
       </c>
       <c r="C617" t="n">
         <v>1</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.19.spd-boost</t>
+          <t>v1b.prepared:character.firefly.trace.16.break-boost</t>
         </is>
       </c>
       <c r="E617" t="n">
@@ -20630,14 +20630,14 @@
     </row>
     <row r="618">
       <c r="B618" t="n">
-        <v>22076</v>
+        <v>22073</v>
       </c>
       <c r="C618" t="n">
         <v>1</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.20.effect-res-boost</t>
+          <t>v1b.prepared:character.firefly.trace.17.effect-res-boost</t>
         </is>
       </c>
       <c r="E618" t="n">
@@ -20659,14 +20659,14 @@
     </row>
     <row r="619">
       <c r="B619" t="n">
-        <v>22077</v>
+        <v>22074</v>
       </c>
       <c r="C619" t="n">
         <v>1</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.trace.21.break-boost</t>
+          <t>v1b.prepared:character.firefly.trace.18.break-boost</t>
         </is>
       </c>
       <c r="E619" t="n">
@@ -20688,14 +20688,14 @@
     </row>
     <row r="620">
       <c r="B620" t="n">
-        <v>22078</v>
+        <v>22075</v>
       </c>
       <c r="C620" t="n">
         <v>1</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.01.trace-1</t>
+          <t>v1b.prepared:character.firefly.trace.19.spd-boost</t>
         </is>
       </c>
       <c r="E620" t="n">
@@ -20717,14 +20717,14 @@
     </row>
     <row r="621">
       <c r="B621" t="n">
-        <v>22079</v>
+        <v>22076</v>
       </c>
       <c r="C621" t="n">
         <v>1</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.02.trace-2</t>
+          <t>v1b.prepared:character.firefly.trace.20.effect-res-boost</t>
         </is>
       </c>
       <c r="E621" t="n">
@@ -20746,14 +20746,14 @@
     </row>
     <row r="622">
       <c r="B622" t="n">
-        <v>22080</v>
+        <v>22077</v>
       </c>
       <c r="C622" t="n">
         <v>1</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.03.trace-3</t>
+          <t>v1b.prepared:character.firefly.trace.21.break-boost</t>
         </is>
       </c>
       <c r="E622" t="n">
@@ -20775,14 +20775,14 @@
     </row>
     <row r="623">
       <c r="B623" t="n">
-        <v>22081</v>
+        <v>22078</v>
       </c>
       <c r="C623" t="n">
         <v>1</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.04.trace-4</t>
+          <t>v1b.prepared:character.kafka.trace.01.trace-1</t>
         </is>
       </c>
       <c r="E623" t="n">
@@ -20804,14 +20804,14 @@
     </row>
     <row r="624">
       <c r="B624" t="n">
-        <v>22082</v>
+        <v>22079</v>
       </c>
       <c r="C624" t="n">
         <v>1</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.05.trace-5</t>
+          <t>v1b.prepared:character.kafka.trace.02.trace-2</t>
         </is>
       </c>
       <c r="E624" t="n">
@@ -20833,14 +20833,14 @@
     </row>
     <row r="625">
       <c r="B625" t="n">
-        <v>22083</v>
+        <v>22080</v>
       </c>
       <c r="C625" t="n">
         <v>1</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.06.torture</t>
+          <t>v1b.prepared:character.kafka.trace.03.trace-3</t>
         </is>
       </c>
       <c r="E625" t="n">
@@ -20862,14 +20862,14 @@
     </row>
     <row r="626">
       <c r="B626" t="n">
-        <v>22084</v>
+        <v>22081</v>
       </c>
       <c r="C626" t="n">
         <v>1</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.07.torture</t>
+          <t>v1b.prepared:character.kafka.trace.04.trace-4</t>
         </is>
       </c>
       <c r="E626" t="n">
@@ -20891,14 +20891,14 @@
     </row>
     <row r="627">
       <c r="B627" t="n">
-        <v>22085</v>
+        <v>22082</v>
       </c>
       <c r="C627" t="n">
         <v>1</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.08.plunder</t>
+          <t>v1b.prepared:character.kafka.trace.05.trace-5</t>
         </is>
       </c>
       <c r="E627" t="n">
@@ -20920,14 +20920,14 @@
     </row>
     <row r="628">
       <c r="B628" t="n">
-        <v>22086</v>
+        <v>22083</v>
       </c>
       <c r="C628" t="n">
         <v>1</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.09.plunder</t>
+          <t>v1b.prepared:character.kafka.trace.06.torture</t>
         </is>
       </c>
       <c r="E628" t="n">
@@ -20949,14 +20949,14 @@
     </row>
     <row r="629">
       <c r="B629" t="n">
-        <v>22087</v>
+        <v>22084</v>
       </c>
       <c r="C629" t="n">
         <v>1</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.10.thorns</t>
+          <t>v1b.prepared:character.kafka.trace.07.torture</t>
         </is>
       </c>
       <c r="E629" t="n">
@@ -20978,14 +20978,14 @@
     </row>
     <row r="630">
       <c r="B630" t="n">
-        <v>22088</v>
+        <v>22085</v>
       </c>
       <c r="C630" t="n">
         <v>1</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.11.atk-boost</t>
+          <t>v1b.prepared:character.kafka.trace.08.plunder</t>
         </is>
       </c>
       <c r="E630" t="n">
@@ -21007,14 +21007,14 @@
     </row>
     <row r="631">
       <c r="B631" t="n">
-        <v>22089</v>
+        <v>22086</v>
       </c>
       <c r="C631" t="n">
         <v>1</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.12.effect-hit-rate-boost</t>
+          <t>v1b.prepared:character.kafka.trace.09.plunder</t>
         </is>
       </c>
       <c r="E631" t="n">
@@ -21036,14 +21036,14 @@
     </row>
     <row r="632">
       <c r="B632" t="n">
-        <v>22090</v>
+        <v>22087</v>
       </c>
       <c r="C632" t="n">
         <v>1</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.13.atk-boost</t>
+          <t>v1b.prepared:character.kafka.trace.10.thorns</t>
         </is>
       </c>
       <c r="E632" t="n">
@@ -21065,14 +21065,14 @@
     </row>
     <row r="633">
       <c r="B633" t="n">
-        <v>22091</v>
+        <v>22088</v>
       </c>
       <c r="C633" t="n">
         <v>1</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.14.hp-boost</t>
+          <t>v1b.prepared:character.kafka.trace.11.atk-boost</t>
         </is>
       </c>
       <c r="E633" t="n">
@@ -21094,14 +21094,14 @@
     </row>
     <row r="634">
       <c r="B634" t="n">
-        <v>22092</v>
+        <v>22089</v>
       </c>
       <c r="C634" t="n">
         <v>1</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.15.atk-boost</t>
+          <t>v1b.prepared:character.kafka.trace.12.effect-hit-rate-boost</t>
         </is>
       </c>
       <c r="E634" t="n">
@@ -21123,14 +21123,14 @@
     </row>
     <row r="635">
       <c r="B635" t="n">
-        <v>22093</v>
+        <v>22090</v>
       </c>
       <c r="C635" t="n">
         <v>1</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.16.effect-hit-rate-boost</t>
+          <t>v1b.prepared:character.kafka.trace.13.atk-boost</t>
         </is>
       </c>
       <c r="E635" t="n">
@@ -21152,14 +21152,14 @@
     </row>
     <row r="636">
       <c r="B636" t="n">
-        <v>22094</v>
+        <v>22091</v>
       </c>
       <c r="C636" t="n">
         <v>1</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.17.atk-boost</t>
+          <t>v1b.prepared:character.kafka.trace.14.hp-boost</t>
         </is>
       </c>
       <c r="E636" t="n">
@@ -21181,14 +21181,14 @@
     </row>
     <row r="637">
       <c r="B637" t="n">
-        <v>22095</v>
+        <v>22092</v>
       </c>
       <c r="C637" t="n">
         <v>1</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.18.hp-boost</t>
+          <t>v1b.prepared:character.kafka.trace.15.atk-boost</t>
         </is>
       </c>
       <c r="E637" t="n">
@@ -21210,14 +21210,14 @@
     </row>
     <row r="638">
       <c r="B638" t="n">
-        <v>22096</v>
+        <v>22093</v>
       </c>
       <c r="C638" t="n">
         <v>1</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.19.effect-hit-rate-boost</t>
+          <t>v1b.prepared:character.kafka.trace.16.effect-hit-rate-boost</t>
         </is>
       </c>
       <c r="E638" t="n">
@@ -21239,14 +21239,14 @@
     </row>
     <row r="639">
       <c r="B639" t="n">
-        <v>22097</v>
+        <v>22094</v>
       </c>
       <c r="C639" t="n">
         <v>1</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.trace.20.atk-boost</t>
+          <t>v1b.prepared:character.kafka.trace.17.atk-boost</t>
         </is>
       </c>
       <c r="E639" t="n">
@@ -21268,14 +21268,14 @@
     </row>
     <row r="640">
       <c r="B640" t="n">
-        <v>22098</v>
+        <v>22095</v>
       </c>
       <c r="C640" t="n">
         <v>1</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.01.trace-1</t>
+          <t>v1b.prepared:character.kafka.trace.18.hp-boost</t>
         </is>
       </c>
       <c r="E640" t="n">
@@ -21297,14 +21297,14 @@
     </row>
     <row r="641">
       <c r="B641" t="n">
-        <v>22099</v>
+        <v>22096</v>
       </c>
       <c r="C641" t="n">
         <v>1</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.02.trace-2</t>
+          <t>v1b.prepared:character.kafka.trace.19.effect-hit-rate-boost</t>
         </is>
       </c>
       <c r="E641" t="n">
@@ -21326,14 +21326,14 @@
     </row>
     <row r="642">
       <c r="B642" t="n">
-        <v>22100</v>
+        <v>22097</v>
       </c>
       <c r="C642" t="n">
         <v>1</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.03.trace-3</t>
+          <t>v1b.prepared:character.kafka.trace.20.atk-boost</t>
         </is>
       </c>
       <c r="E642" t="n">
@@ -21355,14 +21355,14 @@
     </row>
     <row r="643">
       <c r="B643" t="n">
-        <v>22101</v>
+        <v>22098</v>
       </c>
       <c r="C643" t="n">
         <v>1</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.04.trace-4</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.01.trace-1</t>
         </is>
       </c>
       <c r="E643" t="n">
@@ -21384,14 +21384,14 @@
     </row>
     <row r="644">
       <c r="B644" t="n">
-        <v>22102</v>
+        <v>22099</v>
       </c>
       <c r="C644" t="n">
         <v>1</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.05.trace-5</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.02.trace-2</t>
         </is>
       </c>
       <c r="E644" t="n">
@@ -21413,14 +21413,14 @@
     </row>
     <row r="645">
       <c r="B645" t="n">
-        <v>22103</v>
+        <v>22100</v>
       </c>
       <c r="C645" t="n">
         <v>1</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.06.false-ending-speedrun</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.03.trace-3</t>
         </is>
       </c>
       <c r="E645" t="n">
@@ -21442,14 +21442,14 @@
     </row>
     <row r="646">
       <c r="B646" t="n">
-        <v>22104</v>
+        <v>22101</v>
       </c>
       <c r="C646" t="n">
         <v>1</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.07.true-ending-unlocked</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.04.trace-4</t>
         </is>
       </c>
       <c r="E646" t="n">
@@ -21471,14 +21471,14 @@
     </row>
     <row r="647">
       <c r="B647" t="n">
-        <v>22105</v>
+        <v>22102</v>
       </c>
       <c r="C647" t="n">
         <v>1</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.08.secret-level-maxed</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.05.trace-5</t>
         </is>
       </c>
       <c r="E647" t="n">
@@ -21500,14 +21500,14 @@
     </row>
     <row r="648">
       <c r="B648" t="n">
-        <v>22106</v>
+        <v>22103</v>
       </c>
       <c r="C648" t="n">
         <v>1</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.09.crit-rate-boost</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.06.false-ending-speedrun</t>
         </is>
       </c>
       <c r="E648" t="n">
@@ -21529,14 +21529,14 @@
     </row>
     <row r="649">
       <c r="B649" t="n">
-        <v>22107</v>
+        <v>22104</v>
       </c>
       <c r="C649" t="n">
         <v>1</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.10.spd-boost</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.07.true-ending-unlocked</t>
         </is>
       </c>
       <c r="E649" t="n">
@@ -21558,14 +21558,14 @@
     </row>
     <row r="650">
       <c r="B650" t="n">
-        <v>22108</v>
+        <v>22105</v>
       </c>
       <c r="C650" t="n">
         <v>1</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.11.crit-rate-boost</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.08.secret-level-maxed</t>
         </is>
       </c>
       <c r="E650" t="n">
@@ -21587,14 +21587,14 @@
     </row>
     <row r="651">
       <c r="B651" t="n">
-        <v>22109</v>
+        <v>22106</v>
       </c>
       <c r="C651" t="n">
         <v>1</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.12.elation-boost</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.09.crit-rate-boost</t>
         </is>
       </c>
       <c r="E651" t="n">
@@ -21616,14 +21616,14 @@
     </row>
     <row r="652">
       <c r="B652" t="n">
-        <v>22110</v>
+        <v>22107</v>
       </c>
       <c r="C652" t="n">
         <v>1</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.13.crit-rate-boost</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.10.spd-boost</t>
         </is>
       </c>
       <c r="E652" t="n">
@@ -21645,14 +21645,14 @@
     </row>
     <row r="653">
       <c r="B653" t="n">
-        <v>22111</v>
+        <v>22108</v>
       </c>
       <c r="C653" t="n">
         <v>1</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.14.spd-boost</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.11.crit-rate-boost</t>
         </is>
       </c>
       <c r="E653" t="n">
@@ -21674,14 +21674,14 @@
     </row>
     <row r="654">
       <c r="B654" t="n">
-        <v>22112</v>
+        <v>22109</v>
       </c>
       <c r="C654" t="n">
         <v>1</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.15.crit-rate-boost</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.12.elation-boost</t>
         </is>
       </c>
       <c r="E654" t="n">
@@ -21703,14 +21703,14 @@
     </row>
     <row r="655">
       <c r="B655" t="n">
-        <v>22113</v>
+        <v>22110</v>
       </c>
       <c r="C655" t="n">
         <v>1</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.16.elation-boost</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.13.crit-rate-boost</t>
         </is>
       </c>
       <c r="E655" t="n">
@@ -21732,14 +21732,14 @@
     </row>
     <row r="656">
       <c r="B656" t="n">
-        <v>22114</v>
+        <v>22111</v>
       </c>
       <c r="C656" t="n">
         <v>1</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.17.spd-boost</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.14.spd-boost</t>
         </is>
       </c>
       <c r="E656" t="n">
@@ -21761,14 +21761,14 @@
     </row>
     <row r="657">
       <c r="B657" t="n">
-        <v>22115</v>
+        <v>22112</v>
       </c>
       <c r="C657" t="n">
         <v>1</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.18.crit-rate-boost</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.15.crit-rate-boost</t>
         </is>
       </c>
       <c r="E657" t="n">
@@ -21790,14 +21790,14 @@
     </row>
     <row r="658">
       <c r="B658" t="n">
-        <v>22116</v>
+        <v>22113</v>
       </c>
       <c r="C658" t="n">
         <v>1</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.trace.19.elation-skill</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.16.elation-boost</t>
         </is>
       </c>
       <c r="E658" t="n">
@@ -21819,14 +21819,14 @@
     </row>
     <row r="659">
       <c r="B659" t="n">
-        <v>23001</v>
+        <v>22114</v>
       </c>
       <c r="C659" t="n">
         <v>1</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.eidolon.1</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.17.spd-boost</t>
         </is>
       </c>
       <c r="E659" t="n">
@@ -21848,14 +21848,14 @@
     </row>
     <row r="660">
       <c r="B660" t="n">
-        <v>23002</v>
+        <v>22115</v>
       </c>
       <c r="C660" t="n">
         <v>1</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.eidolon.2</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.18.crit-rate-boost</t>
         </is>
       </c>
       <c r="E660" t="n">
@@ -21877,14 +21877,14 @@
     </row>
     <row r="661">
       <c r="B661" t="n">
-        <v>23003</v>
+        <v>22116</v>
       </c>
       <c r="C661" t="n">
         <v>1</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.eidolon.3</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.trace.19.elation-skill</t>
         </is>
       </c>
       <c r="E661" t="n">
@@ -21906,14 +21906,14 @@
     </row>
     <row r="662">
       <c r="B662" t="n">
-        <v>23004</v>
+        <v>23001</v>
       </c>
       <c r="C662" t="n">
         <v>1</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.eidolon.4</t>
+          <t>v1b.prepared:character.aglaea.eidolon.1</t>
         </is>
       </c>
       <c r="E662" t="n">
@@ -21935,14 +21935,14 @@
     </row>
     <row r="663">
       <c r="B663" t="n">
-        <v>23005</v>
+        <v>23002</v>
       </c>
       <c r="C663" t="n">
         <v>1</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.eidolon.5</t>
+          <t>v1b.prepared:character.aglaea.eidolon.2</t>
         </is>
       </c>
       <c r="E663" t="n">
@@ -21964,14 +21964,14 @@
     </row>
     <row r="664">
       <c r="B664" t="n">
-        <v>23006</v>
+        <v>23003</v>
       </c>
       <c r="C664" t="n">
         <v>1</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.aglaea.eidolon.6</t>
+          <t>v1b.prepared:character.aglaea.eidolon.3</t>
         </is>
       </c>
       <c r="E664" t="n">
@@ -21993,14 +21993,14 @@
     </row>
     <row r="665">
       <c r="B665" t="n">
-        <v>23007</v>
+        <v>23004</v>
       </c>
       <c r="C665" t="n">
         <v>1</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.eidolon.1</t>
+          <t>v1b.prepared:character.aglaea.eidolon.4</t>
         </is>
       </c>
       <c r="E665" t="n">
@@ -22022,14 +22022,14 @@
     </row>
     <row r="666">
       <c r="B666" t="n">
-        <v>23008</v>
+        <v>23005</v>
       </c>
       <c r="C666" t="n">
         <v>1</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.eidolon.2</t>
+          <t>v1b.prepared:character.aglaea.eidolon.5</t>
         </is>
       </c>
       <c r="E666" t="n">
@@ -22051,14 +22051,14 @@
     </row>
     <row r="667">
       <c r="B667" t="n">
-        <v>23009</v>
+        <v>23006</v>
       </c>
       <c r="C667" t="n">
         <v>1</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.eidolon.3</t>
+          <t>v1b.prepared:character.aglaea.eidolon.6</t>
         </is>
       </c>
       <c r="E667" t="n">
@@ -22080,14 +22080,14 @@
     </row>
     <row r="668">
       <c r="B668" t="n">
-        <v>23010</v>
+        <v>23007</v>
       </c>
       <c r="C668" t="n">
         <v>1</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.eidolon.4</t>
+          <t>v1b.prepared:character.asta.eidolon.1</t>
         </is>
       </c>
       <c r="E668" t="n">
@@ -22109,14 +22109,14 @@
     </row>
     <row r="669">
       <c r="B669" t="n">
-        <v>23011</v>
+        <v>23008</v>
       </c>
       <c r="C669" t="n">
         <v>1</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.eidolon.5</t>
+          <t>v1b.prepared:character.asta.eidolon.2</t>
         </is>
       </c>
       <c r="E669" t="n">
@@ -22138,14 +22138,14 @@
     </row>
     <row r="670">
       <c r="B670" t="n">
-        <v>23012</v>
+        <v>23009</v>
       </c>
       <c r="C670" t="n">
         <v>1</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.asta.eidolon.6</t>
+          <t>v1b.prepared:character.asta.eidolon.3</t>
         </is>
       </c>
       <c r="E670" t="n">
@@ -22167,14 +22167,14 @@
     </row>
     <row r="671">
       <c r="B671" t="n">
-        <v>23013</v>
+        <v>23010</v>
       </c>
       <c r="C671" t="n">
         <v>1</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.eidolon.1</t>
+          <t>v1b.prepared:character.asta.eidolon.4</t>
         </is>
       </c>
       <c r="E671" t="n">
@@ -22196,14 +22196,14 @@
     </row>
     <row r="672">
       <c r="B672" t="n">
-        <v>23014</v>
+        <v>23011</v>
       </c>
       <c r="C672" t="n">
         <v>1</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.eidolon.2</t>
+          <t>v1b.prepared:character.asta.eidolon.5</t>
         </is>
       </c>
       <c r="E672" t="n">
@@ -22225,14 +22225,14 @@
     </row>
     <row r="673">
       <c r="B673" t="n">
-        <v>23015</v>
+        <v>23012</v>
       </c>
       <c r="C673" t="n">
         <v>1</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.eidolon.3</t>
+          <t>v1b.prepared:character.asta.eidolon.6</t>
         </is>
       </c>
       <c r="E673" t="n">
@@ -22254,14 +22254,14 @@
     </row>
     <row r="674">
       <c r="B674" t="n">
-        <v>23016</v>
+        <v>23013</v>
       </c>
       <c r="C674" t="n">
         <v>1</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.eidolon.4</t>
+          <t>v1b.prepared:character.clara.eidolon.1</t>
         </is>
       </c>
       <c r="E674" t="n">
@@ -22283,14 +22283,14 @@
     </row>
     <row r="675">
       <c r="B675" t="n">
-        <v>23017</v>
+        <v>23014</v>
       </c>
       <c r="C675" t="n">
         <v>1</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.eidolon.5</t>
+          <t>v1b.prepared:character.clara.eidolon.2</t>
         </is>
       </c>
       <c r="E675" t="n">
@@ -22312,14 +22312,14 @@
     </row>
     <row r="676">
       <c r="B676" t="n">
-        <v>23018</v>
+        <v>23015</v>
       </c>
       <c r="C676" t="n">
         <v>1</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.clara.eidolon.6</t>
+          <t>v1b.prepared:character.clara.eidolon.3</t>
         </is>
       </c>
       <c r="E676" t="n">
@@ -22341,14 +22341,14 @@
     </row>
     <row r="677">
       <c r="B677" t="n">
-        <v>23019</v>
+        <v>23016</v>
       </c>
       <c r="C677" t="n">
         <v>1</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.eidolon.1</t>
+          <t>v1b.prepared:character.clara.eidolon.4</t>
         </is>
       </c>
       <c r="E677" t="n">
@@ -22370,14 +22370,14 @@
     </row>
     <row r="678">
       <c r="B678" t="n">
-        <v>23020</v>
+        <v>23017</v>
       </c>
       <c r="C678" t="n">
         <v>1</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.eidolon.2</t>
+          <t>v1b.prepared:character.clara.eidolon.5</t>
         </is>
       </c>
       <c r="E678" t="n">
@@ -22399,14 +22399,14 @@
     </row>
     <row r="679">
       <c r="B679" t="n">
-        <v>23021</v>
+        <v>23018</v>
       </c>
       <c r="C679" t="n">
         <v>1</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.eidolon.3</t>
+          <t>v1b.prepared:character.clara.eidolon.6</t>
         </is>
       </c>
       <c r="E679" t="n">
@@ -22428,14 +22428,14 @@
     </row>
     <row r="680">
       <c r="B680" t="n">
-        <v>23022</v>
+        <v>23019</v>
       </c>
       <c r="C680" t="n">
         <v>1</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.eidolon.4</t>
+          <t>v1b.prepared:character.firefly.eidolon.1</t>
         </is>
       </c>
       <c r="E680" t="n">
@@ -22457,14 +22457,14 @@
     </row>
     <row r="681">
       <c r="B681" t="n">
-        <v>23023</v>
+        <v>23020</v>
       </c>
       <c r="C681" t="n">
         <v>1</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.eidolon.5</t>
+          <t>v1b.prepared:character.firefly.eidolon.2</t>
         </is>
       </c>
       <c r="E681" t="n">
@@ -22486,14 +22486,14 @@
     </row>
     <row r="682">
       <c r="B682" t="n">
-        <v>23024</v>
+        <v>23021</v>
       </c>
       <c r="C682" t="n">
         <v>1</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.firefly.eidolon.6</t>
+          <t>v1b.prepared:character.firefly.eidolon.3</t>
         </is>
       </c>
       <c r="E682" t="n">
@@ -22515,14 +22515,14 @@
     </row>
     <row r="683">
       <c r="B683" t="n">
-        <v>23025</v>
+        <v>23022</v>
       </c>
       <c r="C683" t="n">
         <v>1</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.eidolon.1</t>
+          <t>v1b.prepared:character.firefly.eidolon.4</t>
         </is>
       </c>
       <c r="E683" t="n">
@@ -22544,14 +22544,14 @@
     </row>
     <row r="684">
       <c r="B684" t="n">
-        <v>23026</v>
+        <v>23023</v>
       </c>
       <c r="C684" t="n">
         <v>1</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.eidolon.2</t>
+          <t>v1b.prepared:character.firefly.eidolon.5</t>
         </is>
       </c>
       <c r="E684" t="n">
@@ -22573,14 +22573,14 @@
     </row>
     <row r="685">
       <c r="B685" t="n">
-        <v>23027</v>
+        <v>23024</v>
       </c>
       <c r="C685" t="n">
         <v>1</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.eidolon.3</t>
+          <t>v1b.prepared:character.firefly.eidolon.6</t>
         </is>
       </c>
       <c r="E685" t="n">
@@ -22602,14 +22602,14 @@
     </row>
     <row r="686">
       <c r="B686" t="n">
-        <v>23028</v>
+        <v>23025</v>
       </c>
       <c r="C686" t="n">
         <v>1</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.eidolon.4</t>
+          <t>v1b.prepared:character.kafka.eidolon.1</t>
         </is>
       </c>
       <c r="E686" t="n">
@@ -22631,14 +22631,14 @@
     </row>
     <row r="687">
       <c r="B687" t="n">
-        <v>23029</v>
+        <v>23026</v>
       </c>
       <c r="C687" t="n">
         <v>1</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.eidolon.5</t>
+          <t>v1b.prepared:character.kafka.eidolon.2</t>
         </is>
       </c>
       <c r="E687" t="n">
@@ -22660,14 +22660,14 @@
     </row>
     <row r="688">
       <c r="B688" t="n">
-        <v>23030</v>
+        <v>23027</v>
       </c>
       <c r="C688" t="n">
         <v>1</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.kafka.eidolon.6</t>
+          <t>v1b.prepared:character.kafka.eidolon.3</t>
         </is>
       </c>
       <c r="E688" t="n">
@@ -22689,14 +22689,14 @@
     </row>
     <row r="689">
       <c r="B689" t="n">
-        <v>23031</v>
+        <v>23028</v>
       </c>
       <c r="C689" t="n">
         <v>1</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.eidolon.1</t>
+          <t>v1b.prepared:character.kafka.eidolon.4</t>
         </is>
       </c>
       <c r="E689" t="n">
@@ -22718,14 +22718,14 @@
     </row>
     <row r="690">
       <c r="B690" t="n">
-        <v>23032</v>
+        <v>23029</v>
       </c>
       <c r="C690" t="n">
         <v>1</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.eidolon.2</t>
+          <t>v1b.prepared:character.kafka.eidolon.5</t>
         </is>
       </c>
       <c r="E690" t="n">
@@ -22747,14 +22747,14 @@
     </row>
     <row r="691">
       <c r="B691" t="n">
-        <v>23033</v>
+        <v>23030</v>
       </c>
       <c r="C691" t="n">
         <v>1</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.eidolon.3</t>
+          <t>v1b.prepared:character.kafka.eidolon.6</t>
         </is>
       </c>
       <c r="E691" t="n">
@@ -22776,14 +22776,14 @@
     </row>
     <row r="692">
       <c r="B692" t="n">
-        <v>23034</v>
+        <v>23031</v>
       </c>
       <c r="C692" t="n">
         <v>1</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.eidolon.4</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.eidolon.1</t>
         </is>
       </c>
       <c r="E692" t="n">
@@ -22805,14 +22805,14 @@
     </row>
     <row r="693">
       <c r="B693" t="n">
-        <v>23035</v>
+        <v>23032</v>
       </c>
       <c r="C693" t="n">
         <v>1</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.eidolon.5</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.eidolon.2</t>
         </is>
       </c>
       <c r="E693" t="n">
@@ -22834,14 +22834,14 @@
     </row>
     <row r="694">
       <c r="B694" t="n">
-        <v>23036</v>
+        <v>23033</v>
       </c>
       <c r="C694" t="n">
         <v>1</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>v1b.prepared:character.silver-wolf-lv-999.eidolon.6</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.eidolon.3</t>
         </is>
       </c>
       <c r="E694" t="n">
@@ -22863,14 +22863,14 @@
     </row>
     <row r="695">
       <c r="B695" t="n">
-        <v>24002</v>
+        <v>23034</v>
       </c>
       <c r="C695" t="n">
         <v>1</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.asta.astrometry.rule</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.eidolon.4</t>
         </is>
       </c>
       <c r="E695" t="n">
@@ -22892,14 +22892,14 @@
     </row>
     <row r="696">
       <c r="B696" t="n">
-        <v>24003</v>
+        <v>23035</v>
       </c>
       <c r="C696" t="n">
         <v>1</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.asta.charging.slot</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.eidolon.5</t>
         </is>
       </c>
       <c r="E696" t="n">
@@ -22921,14 +22921,14 @@
     </row>
     <row r="697">
       <c r="B697" t="n">
-        <v>24004</v>
+        <v>23036</v>
       </c>
       <c r="C697" t="n">
         <v>1</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.asta.team-atk.modifier</t>
+          <t>v1b.prepared:character.silver-wolf-lv-999.eidolon.6</t>
         </is>
       </c>
       <c r="E697" t="n">
@@ -22950,14 +22950,14 @@
     </row>
     <row r="698">
       <c r="B698" t="n">
-        <v>24006</v>
+        <v>24002</v>
       </c>
       <c r="C698" t="n">
         <v>1</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.asta.astral-blessing.spd-effect</t>
+          <t>v1b.prepared:program.v1b.asta.astrometry.rule</t>
         </is>
       </c>
       <c r="E698" t="n">
@@ -22979,14 +22979,14 @@
     </row>
     <row r="699">
       <c r="B699" t="n">
-        <v>24007</v>
+        <v>24003</v>
       </c>
       <c r="C699" t="n">
         <v>1</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.asta.astral-blessing.program</t>
+          <t>v1b.prepared:program.v1b.asta.charging.slot</t>
         </is>
       </c>
       <c r="E699" t="n">
@@ -23008,14 +23008,14 @@
     </row>
     <row r="700">
       <c r="B700" t="n">
-        <v>24051</v>
+        <v>24004</v>
       </c>
       <c r="C700" t="n">
         <v>1</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.asta-modifier.1</t>
+          <t>v1b.prepared:program.v1b.asta.team-atk.modifier</t>
         </is>
       </c>
       <c r="E700" t="n">
@@ -23037,14 +23037,14 @@
     </row>
     <row r="701">
       <c r="B701" t="n">
-        <v>24052</v>
+        <v>24006</v>
       </c>
       <c r="C701" t="n">
         <v>1</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.asta-modifier.2</t>
+          <t>v1b.prepared:program.v1b.asta.astral-blessing.spd-effect</t>
         </is>
       </c>
       <c r="E701" t="n">
@@ -23066,14 +23066,14 @@
     </row>
     <row r="702">
       <c r="B702" t="n">
-        <v>24053</v>
+        <v>24007</v>
       </c>
       <c r="C702" t="n">
         <v>1</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.asta-modifier.3</t>
+          <t>v1b.prepared:program.v1b.asta.astral-blessing.program</t>
         </is>
       </c>
       <c r="E702" t="n">
@@ -23095,14 +23095,14 @@
     </row>
     <row r="703">
       <c r="B703" t="n">
-        <v>24104</v>
+        <v>24051</v>
       </c>
       <c r="C703" t="n">
         <v>1</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.kafka.shock.effect</t>
+          <t>v1b.prepared:selector.v1b.asta-modifier.1</t>
         </is>
       </c>
       <c r="E703" t="n">
@@ -23124,14 +23124,14 @@
     </row>
     <row r="704">
       <c r="B704" t="n">
-        <v>24105</v>
+        <v>24052</v>
       </c>
       <c r="C704" t="n">
         <v>1</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.kafka.skill.program</t>
+          <t>v1b.prepared:selector.v1b.asta-modifier.2</t>
         </is>
       </c>
       <c r="E704" t="n">
@@ -23153,14 +23153,14 @@
     </row>
     <row r="705">
       <c r="B705" t="n">
-        <v>24106</v>
+        <v>24053</v>
       </c>
       <c r="C705" t="n">
         <v>1</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.kafka.ultimate.program</t>
+          <t>v1b.prepared:selector.v1b.asta-modifier.3</t>
         </is>
       </c>
       <c r="E705" t="n">
@@ -23182,14 +23182,14 @@
     </row>
     <row r="706">
       <c r="B706" t="n">
-        <v>24107</v>
+        <v>24104</v>
       </c>
       <c r="C706" t="n">
         <v>1</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.kafka.follow-up.program</t>
+          <t>v1b.prepared:program.v1b.kafka.shock.effect</t>
         </is>
       </c>
       <c r="E706" t="n">
@@ -23211,14 +23211,14 @@
     </row>
     <row r="707">
       <c r="B707" t="n">
-        <v>24108</v>
+        <v>24105</v>
       </c>
       <c r="C707" t="n">
         <v>1</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.kafka.follow-up.rule</t>
+          <t>v1b.prepared:program.v1b.kafka.skill.program</t>
         </is>
       </c>
       <c r="E707" t="n">
@@ -23240,14 +23240,14 @@
     </row>
     <row r="708">
       <c r="B708" t="n">
-        <v>24109</v>
+        <v>24106</v>
       </c>
       <c r="C708" t="n">
         <v>1</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.kafka.follow-up.used.slot</t>
+          <t>v1b.prepared:program.v1b.kafka.ultimate.program</t>
         </is>
       </c>
       <c r="E708" t="n">
@@ -23269,14 +23269,14 @@
     </row>
     <row r="709">
       <c r="B709" t="n">
-        <v>24151</v>
+        <v>24107</v>
       </c>
       <c r="C709" t="n">
         <v>1</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.kafka-dot.1</t>
+          <t>v1b.prepared:program.v1b.kafka.follow-up.program</t>
         </is>
       </c>
       <c r="E709" t="n">
@@ -23298,14 +23298,14 @@
     </row>
     <row r="710">
       <c r="B710" t="n">
-        <v>24152</v>
+        <v>24108</v>
       </c>
       <c r="C710" t="n">
         <v>1</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.kafka-dot.2</t>
+          <t>v1b.prepared:program.v1b.kafka.follow-up.rule</t>
         </is>
       </c>
       <c r="E710" t="n">
@@ -23327,14 +23327,14 @@
     </row>
     <row r="711">
       <c r="B711" t="n">
-        <v>24153</v>
+        <v>24109</v>
       </c>
       <c r="C711" t="n">
         <v>1</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.kafka-dot.3</t>
+          <t>v1b.prepared:program.v1b.kafka.follow-up.used.slot</t>
         </is>
       </c>
       <c r="E711" t="n">
@@ -23356,14 +23356,14 @@
     </row>
     <row r="712">
       <c r="B712" t="n">
-        <v>24201</v>
+        <v>24151</v>
       </c>
       <c r="C712" t="n">
         <v>1</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.clara.because-were-family.source</t>
+          <t>v1b.prepared:selector.v1b.kafka-dot.1</t>
         </is>
       </c>
       <c r="E712" t="n">
@@ -23385,14 +23385,14 @@
     </row>
     <row r="713">
       <c r="B713" t="n">
-        <v>24204</v>
+        <v>24152</v>
       </c>
       <c r="C713" t="n">
         <v>1</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.clara.counter.program</t>
+          <t>v1b.prepared:selector.v1b.kafka-dot.2</t>
         </is>
       </c>
       <c r="E713" t="n">
@@ -23414,14 +23414,14 @@
     </row>
     <row r="714">
       <c r="B714" t="n">
-        <v>24205</v>
+        <v>24153</v>
       </c>
       <c r="C714" t="n">
         <v>1</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.clara.counter.rule</t>
+          <t>v1b.prepared:selector.v1b.kafka-dot.3</t>
         </is>
       </c>
       <c r="E714" t="n">
@@ -23443,14 +23443,14 @@
     </row>
     <row r="715">
       <c r="B715" t="n">
-        <v>24206</v>
+        <v>24201</v>
       </c>
       <c r="C715" t="n">
         <v>1</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.clara.enhanced-charges.slot</t>
+          <t>v1b.prepared:program.v1b.clara.because-were-family.source</t>
         </is>
       </c>
       <c r="E715" t="n">
@@ -23472,14 +23472,14 @@
     </row>
     <row r="716">
       <c r="B716" t="n">
-        <v>24251</v>
+        <v>24204</v>
       </c>
       <c r="C716" t="n">
         <v>1</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.clara-counter.1</t>
+          <t>v1b.prepared:program.v1b.clara.counter.program</t>
         </is>
       </c>
       <c r="E716" t="n">
@@ -23501,14 +23501,14 @@
     </row>
     <row r="717">
       <c r="B717" t="n">
-        <v>24252</v>
+        <v>24205</v>
       </c>
       <c r="C717" t="n">
         <v>1</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.clara-counter.2</t>
+          <t>v1b.prepared:program.v1b.clara.counter.rule</t>
         </is>
       </c>
       <c r="E717" t="n">
@@ -23530,14 +23530,14 @@
     </row>
     <row r="718">
       <c r="B718" t="n">
-        <v>24303</v>
+        <v>24206</v>
       </c>
       <c r="C718" t="n">
         <v>1</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.firefly.normal-skill.program</t>
+          <t>v1b.prepared:program.v1b.clara.enhanced-charges.slot</t>
         </is>
       </c>
       <c r="E718" t="n">
@@ -23559,14 +23559,14 @@
     </row>
     <row r="719">
       <c r="B719" t="n">
-        <v>24304</v>
+        <v>24251</v>
       </c>
       <c r="C719" t="n">
         <v>1</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.firefly.ultimate.program</t>
+          <t>v1b.prepared:selector.v1b.clara-counter.1</t>
         </is>
       </c>
       <c r="E719" t="n">
@@ -23588,14 +23588,14 @@
     </row>
     <row r="720">
       <c r="B720" t="n">
-        <v>24305</v>
+        <v>24252</v>
       </c>
       <c r="C720" t="n">
         <v>1</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.firefly.redmode.effect</t>
+          <t>v1b.prepared:selector.v1b.clara-counter.2</t>
         </is>
       </c>
       <c r="E720" t="n">
@@ -23617,14 +23617,14 @@
     </row>
     <row r="721">
       <c r="B721" t="n">
-        <v>24308</v>
+        <v>24303</v>
       </c>
       <c r="C721" t="n">
         <v>1</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.firefly.break.program</t>
+          <t>v1b.prepared:program.v1b.firefly.normal-skill.program</t>
         </is>
       </c>
       <c r="E721" t="n">
@@ -23646,14 +23646,14 @@
     </row>
     <row r="722">
       <c r="B722" t="n">
-        <v>24309</v>
+        <v>24304</v>
       </c>
       <c r="C722" t="n">
         <v>1</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.firefly.complete-combustion-countdown</t>
+          <t>v1b.prepared:program.v1b.firefly.ultimate.program</t>
         </is>
       </c>
       <c r="E722" t="n">
@@ -23675,14 +23675,14 @@
     </row>
     <row r="723">
       <c r="B723" t="n">
-        <v>24351</v>
+        <v>24305</v>
       </c>
       <c r="C723" t="n">
         <v>1</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.firefly-damage.1</t>
+          <t>v1b.prepared:program.v1b.firefly.redmode.effect</t>
         </is>
       </c>
       <c r="E723" t="n">
@@ -23704,14 +23704,14 @@
     </row>
     <row r="724">
       <c r="B724" t="n">
-        <v>24352</v>
+        <v>24308</v>
       </c>
       <c r="C724" t="n">
         <v>1</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.firefly-damage.2</t>
+          <t>v1b.prepared:program.v1b.firefly.break.program</t>
         </is>
       </c>
       <c r="E724" t="n">
@@ -23733,14 +23733,14 @@
     </row>
     <row r="725">
       <c r="B725" t="n">
-        <v>24402</v>
+        <v>24309</v>
       </c>
       <c r="C725" t="n">
         <v>1</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.firefly-transform.complete-combustion.form</t>
+          <t>v1b.prepared:program.v1b.firefly.complete-combustion-countdown</t>
         </is>
       </c>
       <c r="E725" t="n">
@@ -23762,14 +23762,14 @@
     </row>
     <row r="726">
       <c r="B726" t="n">
-        <v>24405</v>
+        <v>24351</v>
       </c>
       <c r="C726" t="n">
         <v>1</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.firefly-transform.program</t>
+          <t>v1b.prepared:selector.v1b.firefly-damage.1</t>
         </is>
       </c>
       <c r="E726" t="n">
@@ -23791,14 +23791,14 @@
     </row>
     <row r="727">
       <c r="B727" t="n">
-        <v>24451</v>
+        <v>24352</v>
       </c>
       <c r="C727" t="n">
         <v>1</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.firefly-transform.1</t>
+          <t>v1b.prepared:selector.v1b.firefly-damage.2</t>
         </is>
       </c>
       <c r="E727" t="n">
@@ -23820,14 +23820,14 @@
     </row>
     <row r="728">
       <c r="B728" t="n">
-        <v>24505</v>
+        <v>24402</v>
       </c>
       <c r="C728" t="n">
         <v>1</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.aglaea.garmentmaker.form</t>
+          <t>v1b.prepared:program.v1b.firefly-transform.complete-combustion.form</t>
         </is>
       </c>
       <c r="E728" t="n">
@@ -23849,14 +23849,14 @@
     </row>
     <row r="729">
       <c r="B729" t="n">
-        <v>24506</v>
+        <v>24405</v>
       </c>
       <c r="C729" t="n">
         <v>1</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.aglaea.memosprite.program</t>
+          <t>v1b.prepared:program.v1b.firefly-transform.program</t>
         </is>
       </c>
       <c r="E729" t="n">
@@ -23878,14 +23878,14 @@
     </row>
     <row r="730">
       <c r="B730" t="n">
-        <v>24507</v>
+        <v>24451</v>
       </c>
       <c r="C730" t="n">
         <v>1</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.aglaea.garmentmaker-action</t>
+          <t>v1b.prepared:selector.v1b.firefly-transform.1</t>
         </is>
       </c>
       <c r="E730" t="n">
@@ -23907,14 +23907,14 @@
     </row>
     <row r="731">
       <c r="B731" t="n">
-        <v>24551</v>
+        <v>24505</v>
       </c>
       <c r="C731" t="n">
         <v>1</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.aglaea-memosprite.1</t>
+          <t>v1b.prepared:program.v1b.aglaea.garmentmaker.form</t>
         </is>
       </c>
       <c r="E731" t="n">
@@ -23936,14 +23936,14 @@
     </row>
     <row r="732">
       <c r="B732" t="n">
-        <v>24552</v>
+        <v>24506</v>
       </c>
       <c r="C732" t="n">
         <v>1</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.aglaea-memosprite.2</t>
+          <t>v1b.prepared:program.v1b.aglaea.memosprite.program</t>
         </is>
       </c>
       <c r="E732" t="n">
@@ -23965,14 +23965,14 @@
     </row>
     <row r="733">
       <c r="B733" t="n">
-        <v>24601</v>
+        <v>24507</v>
       </c>
       <c r="C733" t="n">
         <v>1</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>v1b.prepared:program.v1b.firefly.complete-combustion</t>
+          <t>v1b.prepared:program.v1b.aglaea.garmentmaker-action</t>
         </is>
       </c>
       <c r="E733" t="n">
@@ -23994,14 +23994,14 @@
     </row>
     <row r="734">
       <c r="B734" t="n">
-        <v>24610</v>
+        <v>24551</v>
       </c>
       <c r="C734" t="n">
         <v>1</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>v1b.prepared:ability.v1b.aglaea.garmentmaker-action</t>
+          <t>v1b.prepared:selector.v1b.aglaea-memosprite.1</t>
         </is>
       </c>
       <c r="E734" t="n">
@@ -24023,14 +24023,14 @@
     </row>
     <row r="735">
       <c r="B735" t="n">
-        <v>24611</v>
+        <v>24552</v>
       </c>
       <c r="C735" t="n">
         <v>1</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>v1b.prepared:ability.v1b.firefly.complete-combustion-countdown</t>
+          <t>v1b.prepared:selector.v1b.aglaea-memosprite.2</t>
         </is>
       </c>
       <c r="E735" t="n">
@@ -24052,14 +24052,14 @@
     </row>
     <row r="736">
       <c r="B736" t="n">
-        <v>24701</v>
+        <v>24601</v>
       </c>
       <c r="C736" t="n">
         <v>1</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.aglaea.trace.09.dmg-boost-lightning.ThunderAddedRatio</t>
+          <t>v1b.prepared:program.v1b.firefly.complete-combustion</t>
         </is>
       </c>
       <c r="E736" t="n">
@@ -24081,14 +24081,14 @@
     </row>
     <row r="737">
       <c r="B737" t="n">
-        <v>24702</v>
+        <v>24610</v>
       </c>
       <c r="C737" t="n">
         <v>1</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.aglaea.trace.10.crit-rate-boost.CriticalChanceBase</t>
+          <t>v1b.prepared:ability.v1b.aglaea.garmentmaker-action</t>
         </is>
       </c>
       <c r="E737" t="n">
@@ -24110,14 +24110,14 @@
     </row>
     <row r="738">
       <c r="B738" t="n">
-        <v>24703</v>
+        <v>24611</v>
       </c>
       <c r="C738" t="n">
         <v>1</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.aglaea.trace.11.dmg-boost-lightning.ThunderAddedRatio</t>
+          <t>v1b.prepared:ability.v1b.firefly.complete-combustion-countdown</t>
         </is>
       </c>
       <c r="E738" t="n">
@@ -24139,14 +24139,14 @@
     </row>
     <row r="739">
       <c r="B739" t="n">
-        <v>24704</v>
+        <v>24620</v>
       </c>
       <c r="C739" t="n">
         <v>1</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.aglaea.trace.12.def-boost.DefenceAddedRatio</t>
+          <t>v1b.prepared:selector.v1b.silver-wolf.owner</t>
         </is>
       </c>
       <c r="E739" t="n">
@@ -24168,14 +24168,14 @@
     </row>
     <row r="740">
       <c r="B740" t="n">
-        <v>24705</v>
+        <v>24623</v>
       </c>
       <c r="C740" t="n">
         <v>1</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.aglaea.trace.13.dmg-boost-lightning.ThunderAddedRatio</t>
+          <t>v1b.prepared:program.v1b.silver-wolf.pro-gamer-move</t>
         </is>
       </c>
       <c r="E740" t="n">
@@ -24197,14 +24197,14 @@
     </row>
     <row r="741">
       <c r="B741" t="n">
-        <v>24706</v>
+        <v>24701</v>
       </c>
       <c r="C741" t="n">
         <v>1</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.aglaea.trace.14.crit-rate-boost.CriticalChanceBase</t>
+          <t>v1b.prepared:modifier.character.aglaea.trace.09.dmg-boost-lightning.ThunderAddedRatio</t>
         </is>
       </c>
       <c r="E741" t="n">
@@ -24226,14 +24226,14 @@
     </row>
     <row r="742">
       <c r="B742" t="n">
-        <v>24707</v>
+        <v>24702</v>
       </c>
       <c r="C742" t="n">
         <v>1</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.aglaea.trace.15.dmg-boost-lightning.ThunderAddedRatio</t>
+          <t>v1b.prepared:modifier.character.aglaea.trace.10.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="E742" t="n">
@@ -24255,14 +24255,14 @@
     </row>
     <row r="743">
       <c r="B743" t="n">
-        <v>24708</v>
+        <v>24703</v>
       </c>
       <c r="C743" t="n">
         <v>1</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.aglaea.trace.16.def-boost.DefenceAddedRatio</t>
+          <t>v1b.prepared:modifier.character.aglaea.trace.11.dmg-boost-lightning.ThunderAddedRatio</t>
         </is>
       </c>
       <c r="E743" t="n">
@@ -24284,14 +24284,14 @@
     </row>
     <row r="744">
       <c r="B744" t="n">
-        <v>24709</v>
+        <v>24704</v>
       </c>
       <c r="C744" t="n">
         <v>1</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.aglaea.trace.17.crit-rate-boost.CriticalChanceBase</t>
+          <t>v1b.prepared:modifier.character.aglaea.trace.12.def-boost.DefenceAddedRatio</t>
         </is>
       </c>
       <c r="E744" t="n">
@@ -24313,14 +24313,14 @@
     </row>
     <row r="745">
       <c r="B745" t="n">
-        <v>24710</v>
+        <v>24705</v>
       </c>
       <c r="C745" t="n">
         <v>1</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.aglaea.trace.18.dmg-boost-lightning.ThunderAddedRatio</t>
+          <t>v1b.prepared:modifier.character.aglaea.trace.13.dmg-boost-lightning.ThunderAddedRatio</t>
         </is>
       </c>
       <c r="E745" t="n">
@@ -24342,14 +24342,14 @@
     </row>
     <row r="746">
       <c r="B746" t="n">
-        <v>24711</v>
+        <v>24706</v>
       </c>
       <c r="C746" t="n">
         <v>1</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.asta.trace.09.dmg-boost-fire.FireAddedRatio</t>
+          <t>v1b.prepared:modifier.character.aglaea.trace.14.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="E746" t="n">
@@ -24371,14 +24371,14 @@
     </row>
     <row r="747">
       <c r="B747" t="n">
-        <v>24712</v>
+        <v>24707</v>
       </c>
       <c r="C747" t="n">
         <v>1</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.asta.trace.10.def-boost.DefenceAddedRatio</t>
+          <t>v1b.prepared:modifier.character.aglaea.trace.15.dmg-boost-lightning.ThunderAddedRatio</t>
         </is>
       </c>
       <c r="E747" t="n">
@@ -24400,14 +24400,14 @@
     </row>
     <row r="748">
       <c r="B748" t="n">
-        <v>24713</v>
+        <v>24708</v>
       </c>
       <c r="C748" t="n">
         <v>1</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.asta.trace.11.dmg-boost-fire.FireAddedRatio</t>
+          <t>v1b.prepared:modifier.character.aglaea.trace.16.def-boost.DefenceAddedRatio</t>
         </is>
       </c>
       <c r="E748" t="n">
@@ -24429,14 +24429,14 @@
     </row>
     <row r="749">
       <c r="B749" t="n">
-        <v>24714</v>
+        <v>24709</v>
       </c>
       <c r="C749" t="n">
         <v>1</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.asta.trace.12.crit-rate-boost.CriticalChanceBase</t>
+          <t>v1b.prepared:modifier.character.aglaea.trace.17.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="E749" t="n">
@@ -24458,14 +24458,14 @@
     </row>
     <row r="750">
       <c r="B750" t="n">
-        <v>24715</v>
+        <v>24710</v>
       </c>
       <c r="C750" t="n">
         <v>1</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.asta.trace.13.dmg-boost-fire.FireAddedRatio</t>
+          <t>v1b.prepared:modifier.character.aglaea.trace.18.dmg-boost-lightning.ThunderAddedRatio</t>
         </is>
       </c>
       <c r="E750" t="n">
@@ -24487,14 +24487,14 @@
     </row>
     <row r="751">
       <c r="B751" t="n">
-        <v>24716</v>
+        <v>24711</v>
       </c>
       <c r="C751" t="n">
         <v>1</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.asta.trace.14.def-boost.DefenceAddedRatio</t>
+          <t>v1b.prepared:modifier.character.asta.trace.09.dmg-boost-fire.FireAddedRatio</t>
         </is>
       </c>
       <c r="E751" t="n">
@@ -24516,14 +24516,14 @@
     </row>
     <row r="752">
       <c r="B752" t="n">
-        <v>24717</v>
+        <v>24712</v>
       </c>
       <c r="C752" t="n">
         <v>1</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.asta.trace.15.dmg-boost-fire.FireAddedRatio</t>
+          <t>v1b.prepared:modifier.character.asta.trace.10.def-boost.DefenceAddedRatio</t>
         </is>
       </c>
       <c r="E752" t="n">
@@ -24545,14 +24545,14 @@
     </row>
     <row r="753">
       <c r="B753" t="n">
-        <v>24718</v>
+        <v>24713</v>
       </c>
       <c r="C753" t="n">
         <v>1</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.asta.trace.16.crit-rate-boost.CriticalChanceBase</t>
+          <t>v1b.prepared:modifier.character.asta.trace.11.dmg-boost-fire.FireAddedRatio</t>
         </is>
       </c>
       <c r="E753" t="n">
@@ -24574,14 +24574,14 @@
     </row>
     <row r="754">
       <c r="B754" t="n">
-        <v>24719</v>
+        <v>24714</v>
       </c>
       <c r="C754" t="n">
         <v>1</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.asta.trace.17.def-boost.DefenceAddedRatio</t>
+          <t>v1b.prepared:modifier.character.asta.trace.12.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="E754" t="n">
@@ -24603,14 +24603,14 @@
     </row>
     <row r="755">
       <c r="B755" t="n">
-        <v>24720</v>
+        <v>24715</v>
       </c>
       <c r="C755" t="n">
         <v>1</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.asta.trace.18.dmg-boost-fire.FireAddedRatio</t>
+          <t>v1b.prepared:modifier.character.asta.trace.13.dmg-boost-fire.FireAddedRatio</t>
         </is>
       </c>
       <c r="E755" t="n">
@@ -24632,14 +24632,14 @@
     </row>
     <row r="756">
       <c r="B756" t="n">
-        <v>24721</v>
+        <v>24716</v>
       </c>
       <c r="C756" t="n">
         <v>1</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.clara.trace.09.atk-boost.AttackAddedRatio</t>
+          <t>v1b.prepared:modifier.character.asta.trace.14.def-boost.DefenceAddedRatio</t>
         </is>
       </c>
       <c r="E756" t="n">
@@ -24661,14 +24661,14 @@
     </row>
     <row r="757">
       <c r="B757" t="n">
-        <v>24722</v>
+        <v>24717</v>
       </c>
       <c r="C757" t="n">
         <v>1</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.clara.trace.10.dmg-boost-physical.PhysicalAddedRatio</t>
+          <t>v1b.prepared:modifier.character.asta.trace.15.dmg-boost-fire.FireAddedRatio</t>
         </is>
       </c>
       <c r="E757" t="n">
@@ -24690,14 +24690,14 @@
     </row>
     <row r="758">
       <c r="B758" t="n">
-        <v>24723</v>
+        <v>24718</v>
       </c>
       <c r="C758" t="n">
         <v>1</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.clara.trace.11.atk-boost.AttackAddedRatio</t>
+          <t>v1b.prepared:modifier.character.asta.trace.16.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="E758" t="n">
@@ -24719,14 +24719,14 @@
     </row>
     <row r="759">
       <c r="B759" t="n">
-        <v>24724</v>
+        <v>24719</v>
       </c>
       <c r="C759" t="n">
         <v>1</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.clara.trace.12.hp-boost.HPAddedRatio</t>
+          <t>v1b.prepared:modifier.character.asta.trace.17.def-boost.DefenceAddedRatio</t>
         </is>
       </c>
       <c r="E759" t="n">
@@ -24748,14 +24748,14 @@
     </row>
     <row r="760">
       <c r="B760" t="n">
-        <v>24725</v>
+        <v>24720</v>
       </c>
       <c r="C760" t="n">
         <v>1</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.clara.trace.13.atk-boost.AttackAddedRatio</t>
+          <t>v1b.prepared:modifier.character.asta.trace.18.dmg-boost-fire.FireAddedRatio</t>
         </is>
       </c>
       <c r="E760" t="n">
@@ -24777,14 +24777,14 @@
     </row>
     <row r="761">
       <c r="B761" t="n">
-        <v>24726</v>
+        <v>24721</v>
       </c>
       <c r="C761" t="n">
         <v>1</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.clara.trace.14.dmg-boost-physical.PhysicalAddedRatio</t>
+          <t>v1b.prepared:modifier.character.clara.trace.09.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="E761" t="n">
@@ -24806,14 +24806,14 @@
     </row>
     <row r="762">
       <c r="B762" t="n">
-        <v>24727</v>
+        <v>24722</v>
       </c>
       <c r="C762" t="n">
         <v>1</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.clara.trace.15.atk-boost.AttackAddedRatio</t>
+          <t>v1b.prepared:modifier.character.clara.trace.10.dmg-boost-physical.PhysicalAddedRatio</t>
         </is>
       </c>
       <c r="E762" t="n">
@@ -24835,14 +24835,14 @@
     </row>
     <row r="763">
       <c r="B763" t="n">
-        <v>24728</v>
+        <v>24723</v>
       </c>
       <c r="C763" t="n">
         <v>1</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.clara.trace.16.hp-boost.HPAddedRatio</t>
+          <t>v1b.prepared:modifier.character.clara.trace.11.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="E763" t="n">
@@ -24864,14 +24864,14 @@
     </row>
     <row r="764">
       <c r="B764" t="n">
-        <v>24729</v>
+        <v>24724</v>
       </c>
       <c r="C764" t="n">
         <v>1</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.clara.trace.17.dmg-boost-physical.PhysicalAddedRatio</t>
+          <t>v1b.prepared:modifier.character.clara.trace.12.hp-boost.HPAddedRatio</t>
         </is>
       </c>
       <c r="E764" t="n">
@@ -24893,14 +24893,14 @@
     </row>
     <row r="765">
       <c r="B765" t="n">
-        <v>24730</v>
+        <v>24725</v>
       </c>
       <c r="C765" t="n">
         <v>1</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.clara.trace.18.atk-boost.AttackAddedRatio</t>
+          <t>v1b.prepared:modifier.character.clara.trace.13.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="E765" t="n">
@@ -24922,14 +24922,14 @@
     </row>
     <row r="766">
       <c r="B766" t="n">
-        <v>24731</v>
+        <v>24726</v>
       </c>
       <c r="C766" t="n">
         <v>1</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.firefly.trace.12.break-boost.BreakDamageAddedRatioBase</t>
+          <t>v1b.prepared:modifier.character.clara.trace.14.dmg-boost-physical.PhysicalAddedRatio</t>
         </is>
       </c>
       <c r="E766" t="n">
@@ -24951,14 +24951,14 @@
     </row>
     <row r="767">
       <c r="B767" t="n">
-        <v>24732</v>
+        <v>24727</v>
       </c>
       <c r="C767" t="n">
         <v>1</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.firefly.trace.13.effect-res-boost.StatusResistanceBase</t>
+          <t>v1b.prepared:modifier.character.clara.trace.15.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="E767" t="n">
@@ -24980,14 +24980,14 @@
     </row>
     <row r="768">
       <c r="B768" t="n">
-        <v>24733</v>
+        <v>24728</v>
       </c>
       <c r="C768" t="n">
         <v>1</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.firefly.trace.14.break-boost.BreakDamageAddedRatioBase</t>
+          <t>v1b.prepared:modifier.character.clara.trace.16.hp-boost.HPAddedRatio</t>
         </is>
       </c>
       <c r="E768" t="n">
@@ -25009,14 +25009,14 @@
     </row>
     <row r="769">
       <c r="B769" t="n">
-        <v>24734</v>
+        <v>24729</v>
       </c>
       <c r="C769" t="n">
         <v>1</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.firefly.trace.15.spd-boost.SpeedDelta</t>
+          <t>v1b.prepared:modifier.character.clara.trace.17.dmg-boost-physical.PhysicalAddedRatio</t>
         </is>
       </c>
       <c r="E769" t="n">
@@ -25038,14 +25038,14 @@
     </row>
     <row r="770">
       <c r="B770" t="n">
-        <v>24735</v>
+        <v>24730</v>
       </c>
       <c r="C770" t="n">
         <v>1</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.firefly.trace.16.break-boost.BreakDamageAddedRatioBase</t>
+          <t>v1b.prepared:modifier.character.clara.trace.18.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="E770" t="n">
@@ -25067,14 +25067,14 @@
     </row>
     <row r="771">
       <c r="B771" t="n">
-        <v>24736</v>
+        <v>24731</v>
       </c>
       <c r="C771" t="n">
         <v>1</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.firefly.trace.17.effect-res-boost.StatusResistanceBase</t>
+          <t>v1b.prepared:modifier.character.firefly.trace.12.break-boost.BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="E771" t="n">
@@ -25096,14 +25096,14 @@
     </row>
     <row r="772">
       <c r="B772" t="n">
-        <v>24737</v>
+        <v>24732</v>
       </c>
       <c r="C772" t="n">
         <v>1</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.firefly.trace.18.break-boost.BreakDamageAddedRatioBase</t>
+          <t>v1b.prepared:modifier.character.firefly.trace.13.effect-res-boost.StatusResistanceBase</t>
         </is>
       </c>
       <c r="E772" t="n">
@@ -25125,14 +25125,14 @@
     </row>
     <row r="773">
       <c r="B773" t="n">
-        <v>24738</v>
+        <v>24733</v>
       </c>
       <c r="C773" t="n">
         <v>1</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.firefly.trace.19.spd-boost.SpeedDelta</t>
+          <t>v1b.prepared:modifier.character.firefly.trace.14.break-boost.BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="E773" t="n">
@@ -25154,14 +25154,14 @@
     </row>
     <row r="774">
       <c r="B774" t="n">
-        <v>24739</v>
+        <v>24734</v>
       </c>
       <c r="C774" t="n">
         <v>1</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.firefly.trace.20.effect-res-boost.StatusResistanceBase</t>
+          <t>v1b.prepared:modifier.character.firefly.trace.15.spd-boost.SpeedDelta</t>
         </is>
       </c>
       <c r="E774" t="n">
@@ -25183,14 +25183,14 @@
     </row>
     <row r="775">
       <c r="B775" t="n">
-        <v>24740</v>
+        <v>24735</v>
       </c>
       <c r="C775" t="n">
         <v>1</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.firefly.trace.21.break-boost.BreakDamageAddedRatioBase</t>
+          <t>v1b.prepared:modifier.character.firefly.trace.16.break-boost.BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="E775" t="n">
@@ -25212,14 +25212,14 @@
     </row>
     <row r="776">
       <c r="B776" t="n">
-        <v>24741</v>
+        <v>24736</v>
       </c>
       <c r="C776" t="n">
         <v>1</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.kafka.trace.11.atk-boost.AttackAddedRatio</t>
+          <t>v1b.prepared:modifier.character.firefly.trace.17.effect-res-boost.StatusResistanceBase</t>
         </is>
       </c>
       <c r="E776" t="n">
@@ -25241,14 +25241,14 @@
     </row>
     <row r="777">
       <c r="B777" t="n">
-        <v>24742</v>
+        <v>24737</v>
       </c>
       <c r="C777" t="n">
         <v>1</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.kafka.trace.12.effect-hit-rate-boost.StatusProbabilityBase</t>
+          <t>v1b.prepared:modifier.character.firefly.trace.18.break-boost.BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="E777" t="n">
@@ -25270,14 +25270,14 @@
     </row>
     <row r="778">
       <c r="B778" t="n">
-        <v>24743</v>
+        <v>24738</v>
       </c>
       <c r="C778" t="n">
         <v>1</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.kafka.trace.13.atk-boost.AttackAddedRatio</t>
+          <t>v1b.prepared:modifier.character.firefly.trace.19.spd-boost.SpeedDelta</t>
         </is>
       </c>
       <c r="E778" t="n">
@@ -25299,14 +25299,14 @@
     </row>
     <row r="779">
       <c r="B779" t="n">
-        <v>24744</v>
+        <v>24739</v>
       </c>
       <c r="C779" t="n">
         <v>1</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.kafka.trace.14.hp-boost.HPAddedRatio</t>
+          <t>v1b.prepared:modifier.character.firefly.trace.20.effect-res-boost.StatusResistanceBase</t>
         </is>
       </c>
       <c r="E779" t="n">
@@ -25328,14 +25328,14 @@
     </row>
     <row r="780">
       <c r="B780" t="n">
-        <v>24745</v>
+        <v>24740</v>
       </c>
       <c r="C780" t="n">
         <v>1</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.kafka.trace.15.atk-boost.AttackAddedRatio</t>
+          <t>v1b.prepared:modifier.character.firefly.trace.21.break-boost.BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="E780" t="n">
@@ -25357,14 +25357,14 @@
     </row>
     <row r="781">
       <c r="B781" t="n">
-        <v>24746</v>
+        <v>24741</v>
       </c>
       <c r="C781" t="n">
         <v>1</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.kafka.trace.16.effect-hit-rate-boost.StatusProbabilityBase</t>
+          <t>v1b.prepared:modifier.character.kafka.trace.11.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="E781" t="n">
@@ -25386,14 +25386,14 @@
     </row>
     <row r="782">
       <c r="B782" t="n">
-        <v>24747</v>
+        <v>24742</v>
       </c>
       <c r="C782" t="n">
         <v>1</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.kafka.trace.17.atk-boost.AttackAddedRatio</t>
+          <t>v1b.prepared:modifier.character.kafka.trace.12.effect-hit-rate-boost.StatusProbabilityBase</t>
         </is>
       </c>
       <c r="E782" t="n">
@@ -25415,14 +25415,14 @@
     </row>
     <row r="783">
       <c r="B783" t="n">
-        <v>24748</v>
+        <v>24743</v>
       </c>
       <c r="C783" t="n">
         <v>1</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.kafka.trace.18.hp-boost.HPAddedRatio</t>
+          <t>v1b.prepared:modifier.character.kafka.trace.13.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="E783" t="n">
@@ -25444,14 +25444,14 @@
     </row>
     <row r="784">
       <c r="B784" t="n">
-        <v>24749</v>
+        <v>24744</v>
       </c>
       <c r="C784" t="n">
         <v>1</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.kafka.trace.19.effect-hit-rate-boost.StatusProbabilityBase</t>
+          <t>v1b.prepared:modifier.character.kafka.trace.14.hp-boost.HPAddedRatio</t>
         </is>
       </c>
       <c r="E784" t="n">
@@ -25473,14 +25473,14 @@
     </row>
     <row r="785">
       <c r="B785" t="n">
-        <v>24750</v>
+        <v>24745</v>
       </c>
       <c r="C785" t="n">
         <v>1</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.kafka.trace.20.atk-boost.AttackAddedRatio</t>
+          <t>v1b.prepared:modifier.character.kafka.trace.15.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="E785" t="n">
@@ -25502,14 +25502,14 @@
     </row>
     <row r="786">
       <c r="B786" t="n">
-        <v>24751</v>
+        <v>24746</v>
       </c>
       <c r="C786" t="n">
         <v>1</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.09.crit-rate-boost.CriticalChanceBase</t>
+          <t>v1b.prepared:modifier.character.kafka.trace.16.effect-hit-rate-boost.StatusProbabilityBase</t>
         </is>
       </c>
       <c r="E786" t="n">
@@ -25531,14 +25531,14 @@
     </row>
     <row r="787">
       <c r="B787" t="n">
-        <v>24752</v>
+        <v>24747</v>
       </c>
       <c r="C787" t="n">
         <v>1</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.10.spd-boost.SpeedDelta</t>
+          <t>v1b.prepared:modifier.character.kafka.trace.17.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="E787" t="n">
@@ -25560,14 +25560,14 @@
     </row>
     <row r="788">
       <c r="B788" t="n">
-        <v>24753</v>
+        <v>24748</v>
       </c>
       <c r="C788" t="n">
         <v>1</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.11.crit-rate-boost.CriticalChanceBase</t>
+          <t>v1b.prepared:modifier.character.kafka.trace.18.hp-boost.HPAddedRatio</t>
         </is>
       </c>
       <c r="E788" t="n">
@@ -25589,14 +25589,14 @@
     </row>
     <row r="789">
       <c r="B789" t="n">
-        <v>24754</v>
+        <v>24749</v>
       </c>
       <c r="C789" t="n">
         <v>1</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.12.elation-boost.ElationDamageAddedRatioBase</t>
+          <t>v1b.prepared:modifier.character.kafka.trace.19.effect-hit-rate-boost.StatusProbabilityBase</t>
         </is>
       </c>
       <c r="E789" t="n">
@@ -25618,14 +25618,14 @@
     </row>
     <row r="790">
       <c r="B790" t="n">
-        <v>24755</v>
+        <v>24750</v>
       </c>
       <c r="C790" t="n">
         <v>1</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.13.crit-rate-boost.CriticalChanceBase</t>
+          <t>v1b.prepared:modifier.character.kafka.trace.20.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="E790" t="n">
@@ -25647,14 +25647,14 @@
     </row>
     <row r="791">
       <c r="B791" t="n">
-        <v>24756</v>
+        <v>24751</v>
       </c>
       <c r="C791" t="n">
         <v>1</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.14.spd-boost.SpeedDelta</t>
+          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.09.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="E791" t="n">
@@ -25676,14 +25676,14 @@
     </row>
     <row r="792">
       <c r="B792" t="n">
-        <v>24757</v>
+        <v>24752</v>
       </c>
       <c r="C792" t="n">
         <v>1</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.15.crit-rate-boost.CriticalChanceBase</t>
+          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.10.spd-boost.SpeedDelta</t>
         </is>
       </c>
       <c r="E792" t="n">
@@ -25705,14 +25705,14 @@
     </row>
     <row r="793">
       <c r="B793" t="n">
-        <v>24758</v>
+        <v>24753</v>
       </c>
       <c r="C793" t="n">
         <v>1</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.16.elation-boost.ElationDamageAddedRatioBase</t>
+          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.11.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="E793" t="n">
@@ -25734,14 +25734,14 @@
     </row>
     <row r="794">
       <c r="B794" t="n">
-        <v>24759</v>
+        <v>24754</v>
       </c>
       <c r="C794" t="n">
         <v>1</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.17.spd-boost.SpeedDelta</t>
+          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.12.elation-boost.ElationDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="E794" t="n">
@@ -25763,14 +25763,14 @@
     </row>
     <row r="795">
       <c r="B795" t="n">
-        <v>24760</v>
+        <v>24755</v>
       </c>
       <c r="C795" t="n">
         <v>1</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.18.crit-rate-boost.CriticalChanceBase</t>
+          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.13.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="E795" t="n">
@@ -25792,14 +25792,14 @@
     </row>
     <row r="796">
       <c r="B796" t="n">
-        <v>24990</v>
+        <v>24756</v>
       </c>
       <c r="C796" t="n">
         <v>1</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>v1b.prepared:selector.v1b.trace-minor.owner</t>
+          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.14.spd-boost.SpeedDelta</t>
         </is>
       </c>
       <c r="E796" t="n">
@@ -25821,28 +25821,173 @@
     </row>
     <row r="797">
       <c r="B797" t="n">
+        <v>24757</v>
+      </c>
+      <c r="C797" t="n">
+        <v>1</v>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.15.crit-rate-boost.CriticalChanceBase</t>
+        </is>
+      </c>
+      <c r="E797" t="n">
+        <v>1</v>
+      </c>
+      <c r="F797" t="n">
+        <v>3</v>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="B798" t="n">
+        <v>24758</v>
+      </c>
+      <c r="C798" t="n">
+        <v>1</v>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.16.elation-boost.ElationDamageAddedRatioBase</t>
+        </is>
+      </c>
+      <c r="E798" t="n">
+        <v>1</v>
+      </c>
+      <c r="F798" t="n">
+        <v>3</v>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="B799" t="n">
+        <v>24759</v>
+      </c>
+      <c r="C799" t="n">
+        <v>1</v>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.17.spd-boost.SpeedDelta</t>
+        </is>
+      </c>
+      <c r="E799" t="n">
+        <v>1</v>
+      </c>
+      <c r="F799" t="n">
+        <v>3</v>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="B800" t="n">
+        <v>24760</v>
+      </c>
+      <c r="C800" t="n">
+        <v>1</v>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>v1b.prepared:modifier.character.silver-wolf-lv-999.trace.18.crit-rate-boost.CriticalChanceBase</t>
+        </is>
+      </c>
+      <c r="E800" t="n">
+        <v>1</v>
+      </c>
+      <c r="F800" t="n">
+        <v>3</v>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="B801" t="n">
+        <v>24990</v>
+      </c>
+      <c r="C801" t="n">
+        <v>1</v>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>v1b.prepared:selector.v1b.trace-minor.owner</t>
+        </is>
+      </c>
+      <c r="E801" t="n">
+        <v>1</v>
+      </c>
+      <c r="F801" t="n">
+        <v>3</v>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="B802" t="n">
         <v>24991</v>
       </c>
-      <c r="C797" t="n">
-        <v>1</v>
-      </c>
-      <c r="D797" t="inlineStr">
+      <c r="C802" t="n">
+        <v>1</v>
+      </c>
+      <c r="D802" t="inlineStr">
         <is>
           <t>v1b.prepared:selector.v1b.trace-minor.currentsubject</t>
         </is>
       </c>
-      <c r="E797" t="n">
-        <v>1</v>
-      </c>
-      <c r="F797" t="n">
-        <v>3</v>
-      </c>
-      <c r="G797" t="inlineStr">
-        <is>
-          <t>ExactStructured</t>
-        </is>
-      </c>
-      <c r="H797" t="inlineStr">
+      <c r="E802" t="n">
+        <v>1</v>
+      </c>
+      <c r="F802" t="n">
+        <v>3</v>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
         <is>
           <t>ExactStructured</t>
         </is>
